--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2740000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2641400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4842600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2327000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2072200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1781500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2393400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>928300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>958500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>992900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>970400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1017000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1038900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1001200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2152700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1120400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1185900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1229500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1237900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1226300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1220300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1167400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2211100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>982900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,8 +957,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1052,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1372,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,28 +1384,28 @@
         <v>-14900</v>
       </c>
       <c r="E15" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F15" s="3">
         <v>-32200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-17200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-17600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-18400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-19600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-2700</v>
       </c>
       <c r="M15" s="3">
         <v>-2700</v>
@@ -1392,61 +1414,64 @@
         <v>-2700</v>
       </c>
       <c r="O15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P15" s="3">
         <v>-3100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-7800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-3900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="T15" s="3">
-        <v>-5100</v>
       </c>
       <c r="U15" s="3">
         <v>-5100</v>
       </c>
       <c r="V15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="W15" s="3">
         <v>-5000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-5400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1242800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1016000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1495200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>628700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>334800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>217800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>389500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>49600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>58100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>218700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>143600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>231100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>244600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>251400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>198200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>199300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>154300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>304800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>149600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>133700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>144200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>146800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>169100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1497200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1625400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3347400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1698300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1737400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1563700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2003900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>894200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>933800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>967200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>942400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>981400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>989300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>943100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1934000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>976800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>954800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>984900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>986500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1028100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1021000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1013100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1906300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>932600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>940400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>927100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>886200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>859200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>813800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,192 +1726,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-871600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-718000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-772100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-726700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-716200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-418900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-333800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-310200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-336800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-388900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-368800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-456300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-627000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-302600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-349900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-360900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-393600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-321600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-316700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-793900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>717800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2266900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1018900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1090500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>950700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>907600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>533300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>656900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>715600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>664700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>652400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>679900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>546400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>778700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>408400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>710700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>693900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>681600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>690500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>729400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>728600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1179600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>491800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>660700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>618100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>632000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>554100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>546300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,192 +2009,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>625700</v>
+      </c>
+      <c r="E23" s="3">
         <v>907400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2085900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>926200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1010600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>847500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>753000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>475300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>599900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>657000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>605600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>592500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>620500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>486900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>662100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>349700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>652200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>635100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>625500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>634500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>699400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>696400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1112500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>457900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>628700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>580500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>596400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>518300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>510100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E24" s="3">
         <v>217500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>517300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>224500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>245300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>173300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>113100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>161600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>147600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>145300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>149400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>114700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>152200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>80900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>159100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>155000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>152300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>151700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>153200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>170300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>266700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>105300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>220900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>224600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>215300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>169300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>179500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>482400</v>
+      </c>
+      <c r="E26" s="3">
         <v>689900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1568700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>701600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>765400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>646600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>579700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>362200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>458000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>495500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>458100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>447200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>471100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>372100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>509900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>268800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>493100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>480100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>473300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>482700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>546200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>526100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>845800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>352600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>407800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>355900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>381100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>348900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>330600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E27" s="3">
         <v>663800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1516000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>675500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>739100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>620500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>531900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>339700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>434200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>476000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>438800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>428100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>451900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>353400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>473800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>250700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>473400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>461400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>452600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>462100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>525300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>505400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>805300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>332700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>387900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>335800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>360700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>328600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>307800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2578,8 +2638,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2596,12 +2656,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>871600</v>
+      </c>
+      <c r="E32" s="3">
         <v>718000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1261500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>772100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>726700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>716200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1250900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>418900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>333800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>310200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>336800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>388900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>368800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>456300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1271900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>627000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>302600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>349900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>360900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>393600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>321600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>316700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>793900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>474700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>311700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>346600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>289800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>341000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>303600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E33" s="3">
         <v>663800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1516000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>675500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>739100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>620500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>531900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>339700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>434200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>476000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>438800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>428100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>451900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>353400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>473800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>250700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>473400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>461400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>452600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>462100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>525300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>505400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>805300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>332700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>302500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>335800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>360700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>328600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>307800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E35" s="3">
         <v>663800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1516000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>675500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>739100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>620500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>531900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>339700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>434200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>476000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>438800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>428100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>451900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>353400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>473800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>250700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>473400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>461400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>452600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>462100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>525300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>505400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>805300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>332700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>302500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>335800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>360700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>328600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>307800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,192 +3416,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1731000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1768900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1848400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1817700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1517200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2255800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1688300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1411500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1337600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1479700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1410500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1259000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1552700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1489200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1354800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1298200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1432800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1818900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1271600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1267300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1605400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1311600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1367600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29302000</v>
+      </c>
+      <c r="E42" s="3">
         <v>31423900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>28434800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23674400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26011500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26355800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34545200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>36693900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>42805700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39540100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35042600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32563700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>25206500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23058400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>23893000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11799100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8588100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14306400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10267200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8580300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9113500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7226000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7424000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,8 +3984,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3975,192 +4079,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1739000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1681100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1673000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1664000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1653600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1620300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1134700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1144800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1117900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1116700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1148900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1161600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1146700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1155300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1154600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1140900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1074200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1066500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1044800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>647400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>634400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>637800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>628700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>646500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>656700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>673600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>672800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>675300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8612000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8627400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8642300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8682300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8699500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8728300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8746700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4595900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4597100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4599100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4601800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4604500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4607300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4610400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4614300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4618200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4622100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4626500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4631500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4637100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4640200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4645500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4651700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,8 +4459,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4435,8 +4554,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208264000</v>
+      </c>
+      <c r="E54" s="3">
         <v>209124300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>207671700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>202956400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>200729800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>197955500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>204032900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>149863600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>155107200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>151901200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>150622700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>150481100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>142601100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>138626700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>139537000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>124577800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>119872800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>125500900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>121554900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>120025200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120097400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>116827600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118426100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,100 +4816,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4516000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4945900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4487900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4045800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4377500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4476500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3743300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2174900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2127900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2067200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2042900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2166400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1719500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2095300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2033400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1762800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1562200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1388700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1346500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1446700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1489800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1663800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4871,8 +5004,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4918,24 +5054,24 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>487600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>424900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>422400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>420000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4945,8 +5081,8 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -4963,8 +5099,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,100 +5194,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8201000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7123400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7416600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7462900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3964500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3459300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3017400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3443600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3485400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3500400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3499400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3498500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4382200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5458900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6321300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6321400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6986200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7002500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7655500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8476000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8444900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9140300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8382300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5239,8 +5384,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181307000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182927800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>181870800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>177579200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>175411900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>172699000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>178238400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>131987500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>137203800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>134372400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>133902400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>134034600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>126413800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>122525700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>123591900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>108762000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>104156100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>109721100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>105863100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>104437700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>104637200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>101391600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>102848200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,13 +5989,16 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="E70" s="3">
         <v>2010600</v>
@@ -5849,7 +6016,7 @@
         <v>2010600</v>
       </c>
       <c r="J70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="K70" s="3">
         <v>1750000</v>
@@ -5858,7 +6025,7 @@
         <v>1750000</v>
       </c>
       <c r="M70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="N70" s="3">
         <v>1250000</v>
@@ -5882,7 +6049,7 @@
         <v>1250000</v>
       </c>
       <c r="U70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="V70" s="3">
         <v>1231500</v>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>1231500</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>1231500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17524000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17284400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16836800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16212100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15754000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15219800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14808600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14830700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14646400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14365900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14030200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13731900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13444400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13132400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12919300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12837400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12820900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12490200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12162300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11842400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11516700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11128300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10763600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24946000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24185900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23790300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23366600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23307400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23245900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23783900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16126000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16153400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15778800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15470300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15196500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14937300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14851000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14695100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14565800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14466600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14529800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14460300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14356000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14228700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14204600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14346400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E81" s="3">
         <v>663800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1516000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>675500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>739100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>620500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>531900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>339700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>434200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>476000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>438800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>428100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>451900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>353400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>473800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>250700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>473400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>461400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>452600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>462100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>525300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>505400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>805300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>332700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>302500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>335800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>360700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>328600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>307800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E83" s="3">
         <v>92900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>181000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>92700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>103200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>154600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>57000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>59100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>116600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>58700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>58500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>58800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>56100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>56000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>30000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>67100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>33900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>35600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>36200</v>
       </c>
       <c r="AF83" s="3">
         <v>36200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1419600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1685100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>427800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>953600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1137000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2483100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1295800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>696900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>486300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>537000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>994700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>664100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>131100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-394400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1130700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>746700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>66900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>413300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>550200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1018400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>521200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>484200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>716100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>442600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>337500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>111300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7681,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-87800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-87600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-62000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-93700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-51500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-58500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-51900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-30700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-38400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>682900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1907400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6649500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1747700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6219300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14038600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4195600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-50600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>967300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4726700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-852100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>271300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>873700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>663000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>514500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,100 +8096,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-215700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-216000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-436400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-220500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-205100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-209100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-369800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-156700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-154700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-141800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-141700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-142000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-141900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-141500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-284700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-143200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-145200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-132900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-134400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-139600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-139000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-143800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-227600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,100 +8474,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1520800</v>
+      </c>
+      <c r="E100" s="3">
         <v>408300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5292500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1617400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1976000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2614400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>778700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-335900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7644300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3442900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-826800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18731700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4108700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3219600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>789600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2690400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8416,96 +8664,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-79500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>328100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>297500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-735600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>567500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>350700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>73900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-142100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>69200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>150500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-292800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>134400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-81500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-138100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-382800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>547500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-338200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>293800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-57500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>52600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>58500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,217 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2745000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2740000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2641400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4842600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2327000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2072200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1781500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2393400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>928300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>958500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>992900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>970400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1017000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1038900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1001200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2152700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1120400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1185900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1229500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1237900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1226300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1220300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1167400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>982900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,8 +966,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1064,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,40 +1394,43 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-14900</v>
+        <v>-15000</v>
       </c>
       <c r="E15" s="3">
         <v>-14900</v>
       </c>
       <c r="F15" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="G15" s="3">
         <v>-32200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-17200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-17600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-18400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-19600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-2700</v>
       </c>
       <c r="N15" s="3">
         <v>-2700</v>
@@ -1417,61 +1439,64 @@
         <v>-2700</v>
       </c>
       <c r="P15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-3900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-7800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-3900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="U15" s="3">
-        <v>-5100</v>
       </c>
       <c r="V15" s="3">
         <v>-5100</v>
       </c>
       <c r="W15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="X15" s="3">
         <v>-5000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1242800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1016000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1495200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>628700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>334800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>217800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>389500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>218700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>143600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>231100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>244600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>251400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>198200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>199300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>154300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>304800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>149600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>133700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>144200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>146800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>169100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1497200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1625400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3347400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1698300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1737400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1563700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2003900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>894200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>933800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>967200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>942400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>981400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>989300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>943100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1934000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>976800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>954800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>984900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>986500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1028100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1021000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1013100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>932600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>940400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>927100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>886200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>859200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>813800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,198 +1759,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-816000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-871600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-718000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-772100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-726700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-716200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-418900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-333800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-310200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-336800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-388900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-368800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-456300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-627000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-302600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-349900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-360900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-393600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-321600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-316700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E21" s="3">
         <v>717800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1000400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2266900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1018900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1090500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>950700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>907600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>533300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>656900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>715600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>664700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>652400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>679900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>546400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>778700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>408400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>710700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>693900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>681600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>690500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>729400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>728600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>491800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>660700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>618100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>632000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>554100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>546300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2012,198 +2051,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E23" s="3">
         <v>625700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>907400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2085900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>926200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1010600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>847500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>753000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>475300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>599900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>657000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>605600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>592500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>620500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>486900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>662100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>349700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>652200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>635100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>625500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>634500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>699400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>696400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>457900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>628700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>580500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>596400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>518300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>510100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E24" s="3">
         <v>143300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>217500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>517300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>224500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>245300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>173300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>113100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>142000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>161600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>147600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>145300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>149400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>114700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>152200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>80900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>159100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>155000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>152300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>151700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>153200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>170300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>266700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>105300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>220900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>224600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>215300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>169300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>179500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E26" s="3">
         <v>482400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>689900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1568700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>701600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>765400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>646600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>579700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>362200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>458000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>495500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>458100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>447200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>471100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>372100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>509900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>268800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>493100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>480100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>473300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>482700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>546200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>526100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>845800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>352600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>407800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>355900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>381100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>348900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>330600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E27" s="3">
         <v>456200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>663800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1516000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>675500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>739100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>620500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>531900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>339700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>434200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>476000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>438800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>428100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>451900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>353400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>473800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>250700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>473400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>461400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>452600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>462100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>525300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>505400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>805300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>332700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>387900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>335800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>360700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>328600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>307800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2641,8 +2701,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2659,12 +2719,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E32" s="3">
         <v>871600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>718000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1261500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>772100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>726700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>716200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1250900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>418900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>333800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>310200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>336800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>388900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>368800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>456300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1271900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>627000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>302600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>349900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>360900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>393600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>321600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>316700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>793900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>474700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>311700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>346600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>289800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>341000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>303600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E33" s="3">
         <v>456200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>663800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1516000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>675500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>739100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>620500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>531900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>339700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>434200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>476000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>438800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>428100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>451900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>353400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>473800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>250700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>473400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>461400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>452600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>462100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>525300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>505400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>805300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>332700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>302500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>335800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>360700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>328600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>307800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E35" s="3">
         <v>456200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>663800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1516000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>675500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>739100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>620500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>531900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>339700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>434200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>476000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>438800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>428100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>451900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>353400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>473800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>250700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>473400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>461400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>452600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>462100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>525300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>505400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>805300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>332700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>302500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>335800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>360700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>328600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>307800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,198 +3502,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1695000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1731000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1768900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1848400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1817700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1517200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2255800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1688300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1411500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1337600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1479700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1410500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1259000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1552700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1489200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1354800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1298200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1432800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1818900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1271600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1267300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1605400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1311600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>33527000</v>
+      </c>
+      <c r="E42" s="3">
         <v>29302000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31423900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>28434800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23674400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26011500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26355800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>34545200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36693900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>42805700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>39540100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>35042600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32563700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25206500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>23058400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>23893000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11799100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8588100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14306400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10267200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8580300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9113500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7226000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,8 +4088,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4082,198 +4186,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1739000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1681100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1673000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1664000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1653600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1620300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1134700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1144800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1117900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1116700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1148900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1161600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1146700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1155300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1154600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1140900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1074200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1066500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1044800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>647400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>634400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>637800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>628700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>646500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>656700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>673600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>672800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>675300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8597000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8612000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8627400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8642300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8682300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8699500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8728300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8746700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4595900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4597100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4599100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4601800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4604500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4607300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4610400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4614300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4618200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4622100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4626500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4631500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4637100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4640200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4645500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,8 +4578,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4557,8 +4676,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>215137000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208264000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>209124300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>207671700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>202956400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>200729800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>197955500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>204032900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>149863600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>155107200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>151901200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>150622700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150481100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>142601100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138626700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>139537000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>124577800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>119872800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>125500900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>121554900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120025200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120097400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116827600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,126 +4946,130 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4527000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4516000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4945900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4487900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4045800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4377500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4476500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3743300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2174900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2127900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2067200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2042900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2166400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1719500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2095300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2033400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1762800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1562200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1388700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1346500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1446700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1489800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+        <v>5843000</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>4299100</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5007,8 +5140,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5057,24 +5193,24 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>487600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>424900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>422400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>420000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5084,8 +5220,8 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5102,8 +5238,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,103 +5336,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8201000</v>
+        <v>11450000</v>
       </c>
       <c r="E61" s="3">
+        <v>7674000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7123400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7416600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7462900</v>
       </c>
-      <c r="H61" s="3">
-        <v>3964500</v>
-      </c>
       <c r="I61" s="3">
+        <v>3220400</v>
+      </c>
+      <c r="J61" s="3">
         <v>3459300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3017400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3443600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3485400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3500400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3499400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3498500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4382200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5458900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6321300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6321400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6986200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7002500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7655500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8476000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8444900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9140300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5387,8 +5532,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>187968000</v>
+      </c>
+      <c r="E66" s="3">
         <v>181307000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>182927800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>181870800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>177579200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>175411900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>172699000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>178238400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>131987500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137203800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>134372400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>133902400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>134034600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>126413800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>122525700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>123591900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>108762000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>104156100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>109721100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>105863100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>104437700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>104637200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>101391600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6001,7 +6168,7 @@
         <v>2011000</v>
       </c>
       <c r="E70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="F70" s="3">
         <v>2010600</v>
@@ -6019,7 +6186,7 @@
         <v>2010600</v>
       </c>
       <c r="K70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="L70" s="3">
         <v>1750000</v>
@@ -6028,7 +6195,7 @@
         <v>1750000</v>
       </c>
       <c r="N70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="O70" s="3">
         <v>1250000</v>
@@ -6052,7 +6219,7 @@
         <v>1250000</v>
       </c>
       <c r="V70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="W70" s="3">
         <v>1231500</v>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>1231500</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>1231500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17812000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17524000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17284400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16836800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16212100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15754000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15219800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14808600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14830700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14646400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14365900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14030200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13731900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13444400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13132400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12919300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12837400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12820900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12490200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12162300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11842400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11516700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11128300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25158000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24946000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24185900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23790300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23366600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23307400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23245900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23783900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16126000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16153400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15778800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15470300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15196500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14937300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14851000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14695100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14565800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14466600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14529800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14460300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14356000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14228700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14204600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E81" s="3">
         <v>456200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>663800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1516000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>675500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>739100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>620500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>531900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>339700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>434200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>476000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>438800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>428100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>451900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>353400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>473800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>250700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>473400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>461400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>452600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>462100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>525300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>505400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>805300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>332700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>302500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>335800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>360700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>328600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>307800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E83" s="3">
         <v>92100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>92900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>181000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>92700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>103200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>154600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>58000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>57000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>116600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>58700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>58500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>58800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>56100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>56000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>30000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>67100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>33900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>37500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>35600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>36200</v>
       </c>
       <c r="AG83" s="3">
         <v>36200</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>608000</v>
+      </c>
+      <c r="E89" s="3">
         <v>800300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1419600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1685100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>427800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>953600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1137000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2483100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1295800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>696900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>486300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>537000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>994700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>664100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>131100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-394400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1130700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>746700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>66900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>413300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>550200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1018400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>521200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>484200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>716100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>442600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>337500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>111300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,103 +7901,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-87800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-87600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-62000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-93700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-51500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-58500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-51900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7082000</v>
+      </c>
+      <c r="E94" s="3">
         <v>682900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1907400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6649500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1747700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6219300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14038600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4195600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-50600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>967300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4726700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-852100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>271300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>873700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>663000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>514500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,103 +8329,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-215700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-216000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-436400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-220500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-205100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-209100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-369800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-156700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-154700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-141800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-141700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-142000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-141900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-284700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-143200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-145200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-132900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-134400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-139600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-139000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-143800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,103 +8719,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6438000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1520800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>408300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5292500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1617400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1976000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2614400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>778700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-335900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7644300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3442900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-826800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18731700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4108700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3219600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>789600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2690400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8667,99 +8915,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-79500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>328100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>297500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-735600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>567500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>350700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>73900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-142100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>69200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>150500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-292800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>134400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-81500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-138100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-382800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>547500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-338200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>293800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-57500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>52600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>58500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2789000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2745000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2740000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2641400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4842600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2327000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2072200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1781500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2393400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>928300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>958500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>992900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>970400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1017000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1038900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1001200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2152700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1120400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1185900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1229500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1237900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1226300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1220300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>982900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,8 +1076,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,43 +1416,46 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E15" s="3">
         <v>-15000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-14900</v>
       </c>
       <c r="F15" s="3">
         <v>-14900</v>
       </c>
       <c r="G15" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="H15" s="3">
         <v>-32200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-17200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-17600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-18400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-19600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-2700</v>
       </c>
       <c r="O15" s="3">
         <v>-2700</v>
@@ -1442,61 +1464,64 @@
         <v>-2700</v>
       </c>
       <c r="Q15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="R15" s="3">
         <v>-3100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-3900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-7800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-3900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="V15" s="3">
-        <v>-5100</v>
       </c>
       <c r="W15" s="3">
         <v>-5100</v>
       </c>
       <c r="X15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1221000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1265000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1242800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1016000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1495200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>628700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>334800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>217800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>389500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>58100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>218700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>143600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>231100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>244600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>251400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>198200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>199300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>154300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>304800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>149600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>133700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>144200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>146800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>169100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1568000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1480000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1497200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1625400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3347400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1698300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1737400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1563700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2003900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>894200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>933800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>967200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>942400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>981400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>989300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>943100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1934000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>976800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>954800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>984900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>986500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1028100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1021000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>932600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>940400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>927100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>886200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>859200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>813800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,204 +1792,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-713000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-816000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-871600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-718000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-772100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-726700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-716200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-418900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-333800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-310200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-336800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-388900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-368800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-456300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-627000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-302600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-349900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-360900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-393600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-321600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>947000</v>
+      </c>
+      <c r="E21" s="3">
         <v>759000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>717800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1000400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2266900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1018900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1090500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>950700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>907600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>533300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>656900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>715600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>664700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>652400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>679900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>546400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>778700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>408400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>710700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>693900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>681600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>690500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>729400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>728600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>491800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>660700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>618100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>632000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>554100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>546300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2054,204 +2093,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>855000</v>
+      </c>
+      <c r="E23" s="3">
         <v>664000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>625700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>907400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2085900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>926200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1010600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>847500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>753000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>475300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>599900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>657000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>605600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>592500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>620500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>486900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>662100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>349700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>652200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>635100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>625500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>634500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>699400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>696400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>457900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>628700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>580500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>596400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>518300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>510100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E24" s="3">
         <v>133000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>143300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>217500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>517300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>224500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>245300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>173300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>113100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>142000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>161600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>147600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>145300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>149400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>114700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>152200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>80900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>159100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>155000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>152300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>151700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>153200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>170300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>266700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>105300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>220900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>224600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>215300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>169300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>179500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E26" s="3">
         <v>531000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>482400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>689900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1568700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>701600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>765400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>646600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>579700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>362200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>458000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>495500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>458100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>447200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>471100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>372100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>509900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>268800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>493100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>480100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>473300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>482700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>546200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>526100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>845800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>352600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>407800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>355900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>381100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>348900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>330600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E27" s="3">
         <v>505000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>456200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>663800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1516000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>675500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>739100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>620500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>531900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>339700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>434200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>476000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>438800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>428100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>451900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>353400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>473800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>250700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>473400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>461400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>452600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>462100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>525300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>505400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>805300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>332700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>387900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>335800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>360700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>328600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>307800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2704,8 +2764,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2722,12 +2782,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E32" s="3">
         <v>816000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>871600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>718000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1261500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>772100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>726700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>716200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1250900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>418900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>333800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>310200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>336800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>388900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>368800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>456300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1271900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>627000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>302600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>349900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>360900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>393600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>321600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>316700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>793900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>474700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>311700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>346600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>289800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>341000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>303600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E33" s="3">
         <v>505000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>456200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>663800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1516000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>675500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>739100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>620500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>531900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>339700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>434200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>476000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>438800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>428100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>451900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>353400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>473800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>250700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>473400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>461400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>452600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>462100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>525300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>505400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>805300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>332700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>302500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>335800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>360700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>328600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>307800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E35" s="3">
         <v>505000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>456200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>663800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1516000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>675500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>739100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>620500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>531900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>339700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>434200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>476000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>438800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>428100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>451900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>353400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>473800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>250700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>473400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>461400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>452600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>462100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>525300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>505400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>805300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>332700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>302500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>335800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>360700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>328600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>307800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,204 +3588,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1778000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1695000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1731000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1768900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1848400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1817700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1517200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2255800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1688300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1411500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1337600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1479700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1410500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1259000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1552700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1489200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1354800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1298200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1432800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1818900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1271600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1267300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1605400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26100000</v>
+      </c>
+      <c r="E42" s="3">
         <v>33527000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29302000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31423900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28434800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>23674400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26011500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26355800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>34545200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36693900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>42805700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39540100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>35042600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>32563700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25206500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>23058400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>23893000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11799100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8588100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14306400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10267200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8580300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9113500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,8 +4192,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4189,204 +4293,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1719000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1707000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1739000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1681100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1673000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1664000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1653600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1620300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1600200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1134700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1144800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1117900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1116700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1148900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1161600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1146700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1155300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1154600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1140900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1074200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1066500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1044800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>647400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>634400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>637800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>628700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>646500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>656700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>673600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>672800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>675300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8597000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8612000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8627400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8642300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8682300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8699500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8728300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8746700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4595900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4597100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4599100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4601800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4604500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4607300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4610400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4614300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4618200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4622100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4626500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4631500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4637100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4640200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,8 +4697,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4679,8 +4798,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208855000</v>
+      </c>
+      <c r="E54" s="3">
         <v>215137000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208264000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>209124300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>207671700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>202956400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>200729800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>197955500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>204032900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>149863600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>155107200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>151901200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150622700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>150481100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>142601100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>138626700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>139537000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>124577800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119872800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>125500900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>121554900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120025200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120097400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,132 +5076,136 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4438000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4527000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4516000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4945900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4487900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4045800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4377500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4476500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3743300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2174900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2127900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2067200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2042900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2166400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1719500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2095300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2033400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1762800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1562200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1388700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1346500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1446700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3">
         <v>5843000</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3">
         <v>4299100</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5143,8 +5276,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5196,24 +5332,24 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>487600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>424900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>422400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>420000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5223,8 +5359,8 @@
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5241,8 +5377,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,106 +5478,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11319000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11450000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7674000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7123400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7416600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7462900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3220400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3459300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3017400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3443600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3485400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3500400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3499400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3498500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4382200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5458900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6321300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6321400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6986200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7002500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7655500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8476000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8444900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5535,8 +5680,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>180431000</v>
+      </c>
+      <c r="E66" s="3">
         <v>187968000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>181307000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182927800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>181870800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>177579200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>175411900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>172699000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>178238400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>131987500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>137203800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>134372400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>133902400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>134034600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>126413800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>122525700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>123591900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>108762000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>104156100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>109721100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>105863100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>104437700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>104637200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,19 +6323,22 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>2011000</v>
+        <v>2744000</v>
       </c>
       <c r="E70" s="3">
         <v>2011000</v>
       </c>
       <c r="F70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="G70" s="3">
         <v>2010600</v>
@@ -6189,7 +6356,7 @@
         <v>2010600</v>
       </c>
       <c r="L70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="M70" s="3">
         <v>1750000</v>
@@ -6198,7 +6365,7 @@
         <v>1750000</v>
       </c>
       <c r="O70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="P70" s="3">
         <v>1250000</v>
@@ -6222,7 +6389,7 @@
         <v>1250000</v>
       </c>
       <c r="W70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="X70" s="3">
         <v>1231500</v>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>1231500</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>1231500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18211000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17812000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17524000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17284400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16836800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16212100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15754000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15219800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14808600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14830700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14646400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14365900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14030200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13731900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13444400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13132400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12919300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12837400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12820900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12490200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12162300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11842400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11516700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25680000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25158000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24946000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24185900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23790300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23366600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23307400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23245900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23783900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16126000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16153400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15778800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15470300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15196500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14937300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14851000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14695100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14565800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14466600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14529800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14460300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14356000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14228700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E81" s="3">
         <v>505000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>456200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>663800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1516000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>675500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>739100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>620500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>531900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>339700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>434200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>476000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>438800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>428100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>451900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>353400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>473800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>250700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>473400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>461400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>452600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>462100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>525300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>505400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>805300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>332700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>302500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>335800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>360700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>328600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>307800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E83" s="3">
         <v>95000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>92100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>92900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>181000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>92700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>154600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>57000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>59500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>116600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>58700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>58500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>58800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>56100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>56000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>30000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>67100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>33900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>35600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>36200</v>
       </c>
       <c r="AH83" s="3">
         <v>36200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1354000</v>
+      </c>
+      <c r="E89" s="3">
         <v>608000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>800300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1419600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1685100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>427800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>953600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1137000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2483100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1295800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>696900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>486300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>537000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>994700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>664100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>131100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-394400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1130700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>746700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>66900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>413300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>550200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>521200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>484200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>716100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>442600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>337500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>111300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-87800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-87600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-62000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-93700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-58500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-51900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5625000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>682900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1907400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6649500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1747700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>6219300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14038600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4195600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-50600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>967300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>4726700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-852100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>271300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>873700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>663000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>514500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,106 +8562,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-225000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-221000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-215700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-216000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-436400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-220500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-205100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-209100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-369800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-156700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-154700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-141800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-141700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-142000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-141500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-284700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-143200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-145200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-132900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-134400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-139600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-139000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,106 +8964,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6896000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6438000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1520800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>408300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5292500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1617400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1976000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2614400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>778700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-335900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7644300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3442900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-826800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>18731700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4108700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3219600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>789600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2690400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-36000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-37600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-79500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>328100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>297500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-735600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>567500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>350700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>73900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-142100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>69200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>150500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-292800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>63500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>134400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-81500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-138100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-382800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>547500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-338200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>293800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>52600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>58500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2789000</v>
+        <v>2212000</v>
       </c>
       <c r="E8" s="3">
-        <v>2745000</v>
+        <v>2152000</v>
       </c>
       <c r="F8" s="3">
-        <v>2740000</v>
+        <v>2060000</v>
       </c>
       <c r="G8" s="3">
-        <v>2641400</v>
+        <v>2075300</v>
       </c>
       <c r="H8" s="3">
-        <v>4842600</v>
+        <v>2185000</v>
       </c>
       <c r="I8" s="3">
-        <v>2327000</v>
+        <v>2452000</v>
       </c>
       <c r="J8" s="3">
+        <v>2285000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2072200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1781500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2393400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>928300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>958500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>992900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>970400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1017000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1038900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1001200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2152700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1120400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1185900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1229500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1237900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1226300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>982900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,31 +984,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>2212000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2152000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2060000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2075300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2452000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2285000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1079,8 +1088,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,31 +1334,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,46 +1438,49 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-13000</v>
+        <v>122000</v>
       </c>
       <c r="E15" s="3">
-        <v>-15000</v>
+        <v>127000</v>
       </c>
       <c r="F15" s="3">
-        <v>-14900</v>
+        <v>130000</v>
       </c>
       <c r="G15" s="3">
-        <v>-14900</v>
+        <v>129300</v>
       </c>
       <c r="H15" s="3">
-        <v>-32200</v>
+        <v>130000</v>
       </c>
       <c r="I15" s="3">
-        <v>-17200</v>
+        <v>125000</v>
       </c>
       <c r="J15" s="3">
+        <v>113000</v>
+      </c>
+      <c r="K15" s="3">
         <v>-17600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-18400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-19600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-2700</v>
       </c>
       <c r="P15" s="3">
         <v>-2700</v>
@@ -1467,61 +1489,64 @@
         <v>-2700</v>
       </c>
       <c r="R15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="S15" s="3">
         <v>-3100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-3900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-7800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-3900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="W15" s="3">
-        <v>-5100</v>
       </c>
       <c r="X15" s="3">
         <v>-5100</v>
       </c>
       <c r="Y15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1221000</v>
+        <v>1266000</v>
       </c>
       <c r="E17" s="3">
-        <v>1265000</v>
+        <v>1247000</v>
       </c>
       <c r="F17" s="3">
-        <v>1242800</v>
+        <v>1321000</v>
       </c>
       <c r="G17" s="3">
-        <v>1016000</v>
+        <v>1206800</v>
       </c>
       <c r="H17" s="3">
-        <v>1495200</v>
+        <v>1234000</v>
       </c>
       <c r="I17" s="3">
-        <v>628700</v>
+        <v>1250000</v>
       </c>
       <c r="J17" s="3">
+        <v>1312000</v>
+      </c>
+      <c r="K17" s="3">
         <v>334800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>217800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>389500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>49600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>218700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>143600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>231100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>244600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>251400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>198200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>199300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>154300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>304800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>149600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>133700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>130100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>144200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>146800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>169100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1568000</v>
+        <v>946000</v>
       </c>
       <c r="E18" s="3">
-        <v>1480000</v>
+        <v>905000</v>
       </c>
       <c r="F18" s="3">
-        <v>1497200</v>
+        <v>739000</v>
       </c>
       <c r="G18" s="3">
-        <v>1625400</v>
+        <v>868500</v>
       </c>
       <c r="H18" s="3">
-        <v>3347400</v>
+        <v>951000</v>
       </c>
       <c r="I18" s="3">
-        <v>1698300</v>
+        <v>1202000</v>
       </c>
       <c r="J18" s="3">
+        <v>973000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1737400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1563700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2003900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>894200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>933800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>967200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>942400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>981400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>989300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>943100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1934000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>976800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>954800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>984900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>986500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1028100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>932600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>940400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>927100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>886200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>859200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>813800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,233 +1825,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-713000</v>
+        <v>37000</v>
       </c>
       <c r="E20" s="3">
-        <v>-816000</v>
+        <v>50000</v>
       </c>
       <c r="F20" s="3">
-        <v>-871600</v>
+        <v>75000</v>
       </c>
       <c r="G20" s="3">
-        <v>-718000</v>
+        <v>242800</v>
       </c>
       <c r="H20" s="3">
-        <v>-1261500</v>
+        <v>44000</v>
       </c>
       <c r="I20" s="3">
-        <v>-772100</v>
+        <v>43000</v>
       </c>
       <c r="J20" s="3">
+        <v>47000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-726700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-716200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-418900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-333800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-310200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-336800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-388900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-368800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-456300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-627000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-302600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-349900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-360900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-393600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>947000</v>
+        <v>1031000</v>
       </c>
       <c r="E21" s="3">
-        <v>759000</v>
+        <v>982000</v>
       </c>
       <c r="F21" s="3">
-        <v>717800</v>
+        <v>794000</v>
       </c>
       <c r="G21" s="3">
-        <v>1000400</v>
+        <v>755000</v>
       </c>
       <c r="H21" s="3">
-        <v>2266900</v>
+        <v>1037000</v>
       </c>
       <c r="I21" s="3">
-        <v>1018900</v>
+        <v>1284000</v>
       </c>
       <c r="J21" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1090500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>950700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>907600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>533300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>656900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>715600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>664700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>652400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>679900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>546400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>778700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>408400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>710700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>693900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>681600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>690500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>729400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>728600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>491800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>660700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>618100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>632000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>554100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>546300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2096,210 +2135,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>909000</v>
+      </c>
+      <c r="E23" s="3">
         <v>855000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>664000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>625700</v>
       </c>
-      <c r="G23" s="3">
-        <v>907400</v>
-      </c>
       <c r="H23" s="3">
-        <v>2085900</v>
+        <v>907000</v>
       </c>
       <c r="I23" s="3">
-        <v>926200</v>
+        <v>1159000</v>
       </c>
       <c r="J23" s="3">
+        <v>926000</v>
+      </c>
+      <c r="K23" s="3">
         <v>1010600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>847500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>753000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>475300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>599900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>657000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>605600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>592500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>620500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>486900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>662100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>349700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>652200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>635100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>625500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>634500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>699400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>696400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>457900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>628700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>580500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>596400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>518300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>510100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E24" s="3">
         <v>200000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>133000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>143300</v>
       </c>
-      <c r="G24" s="3">
-        <v>217500</v>
-      </c>
       <c r="H24" s="3">
-        <v>517300</v>
+        <v>217000</v>
       </c>
       <c r="I24" s="3">
-        <v>224500</v>
+        <v>292000</v>
       </c>
       <c r="J24" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K24" s="3">
         <v>245300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>173300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>113100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>142000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>161600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>147600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>145300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>149400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>114700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>152200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>80900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>159100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>155000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>152300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>151700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>153200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>170300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>266700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>105300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>220900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>224600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>215300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>169300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>179500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E26" s="3">
         <v>655000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>531000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>482400</v>
       </c>
-      <c r="G26" s="3">
-        <v>689900</v>
-      </c>
       <c r="H26" s="3">
-        <v>1568700</v>
+        <v>690000</v>
       </c>
       <c r="I26" s="3">
-        <v>701600</v>
+        <v>867000</v>
       </c>
       <c r="J26" s="3">
+        <v>702000</v>
+      </c>
+      <c r="K26" s="3">
         <v>765400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>646600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>579700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>362200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>458000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>495500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>458100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>447200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>471100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>372100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>509900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>268800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>493100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>480100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>473300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>482700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>546200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>526100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>845800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>352600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>407800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>355900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>381100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>348900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>330600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>674000</v>
+      </c>
+      <c r="E27" s="3">
         <v>626000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>505000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>456200</v>
       </c>
-      <c r="G27" s="3">
-        <v>663800</v>
-      </c>
       <c r="H27" s="3">
-        <v>1516000</v>
+        <v>664000</v>
       </c>
       <c r="I27" s="3">
-        <v>675500</v>
+        <v>841000</v>
       </c>
       <c r="J27" s="3">
+        <v>676000</v>
+      </c>
+      <c r="K27" s="3">
         <v>739100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>620500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>531900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>339700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>434200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>476000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>438800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>428100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>451900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>353400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>473800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>250700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>473400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>461400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>452600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>462100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>525300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>505400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>805300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>332700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>387900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>335800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>360700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>328600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>307800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2767,8 +2827,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2785,12 +2845,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>713000</v>
+        <v>-37000</v>
       </c>
       <c r="E32" s="3">
-        <v>816000</v>
+        <v>-50000</v>
       </c>
       <c r="F32" s="3">
-        <v>871600</v>
+        <v>-75000</v>
       </c>
       <c r="G32" s="3">
-        <v>718000</v>
+        <v>-242800</v>
       </c>
       <c r="H32" s="3">
-        <v>1261500</v>
+        <v>-44000</v>
       </c>
       <c r="I32" s="3">
-        <v>772100</v>
+        <v>-43000</v>
       </c>
       <c r="J32" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="K32" s="3">
         <v>726700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>716200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1250900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>418900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>333800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>310200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>336800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>388900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>368800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>456300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1271900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>627000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>302600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>349900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>360900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>393600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>321600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>316700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>793900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>474700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>311700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>346600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>289800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>341000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>303600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>626000</v>
+        <v>721000</v>
       </c>
       <c r="E33" s="3">
-        <v>505000</v>
+        <v>655000</v>
       </c>
       <c r="F33" s="3">
-        <v>456200</v>
+        <v>531000</v>
       </c>
       <c r="G33" s="3">
-        <v>663800</v>
+        <v>482400</v>
       </c>
       <c r="H33" s="3">
-        <v>1516000</v>
+        <v>690000</v>
       </c>
       <c r="I33" s="3">
-        <v>675500</v>
+        <v>867000</v>
       </c>
       <c r="J33" s="3">
+        <v>702000</v>
+      </c>
+      <c r="K33" s="3">
         <v>739100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>620500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>531900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>339700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>434200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>476000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>438800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>428100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>451900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>353400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>473800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>250700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>473400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>461400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>452600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>462100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>525300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>505400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>805300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>332700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>302500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>335800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>360700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>328600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>307800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>626000</v>
+        <v>721000</v>
       </c>
       <c r="E35" s="3">
-        <v>505000</v>
+        <v>655000</v>
       </c>
       <c r="F35" s="3">
-        <v>456200</v>
+        <v>531000</v>
       </c>
       <c r="G35" s="3">
-        <v>663800</v>
+        <v>482400</v>
       </c>
       <c r="H35" s="3">
-        <v>1516000</v>
+        <v>690000</v>
       </c>
       <c r="I35" s="3">
-        <v>675500</v>
+        <v>867000</v>
       </c>
       <c r="J35" s="3">
+        <v>702000</v>
+      </c>
+      <c r="K35" s="3">
         <v>739100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>620500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>531900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>339700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>434200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>476000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>438800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>428100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>451900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>353400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>473800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>250700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>473400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>461400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>452600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>462100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>525300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>505400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>805300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>332700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>302500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>335800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>360700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>328600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>307800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,233 +3674,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1778000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1695000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1731000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1768900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1848400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1817700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1517200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2255800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1688300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1411500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1337600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1479700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1410500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1259000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1552700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1489200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1354800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1298200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1432800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1818900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1271600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1267300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>26100000</v>
+        <v>24783000</v>
       </c>
       <c r="E42" s="3">
-        <v>33527000</v>
+        <v>25164000</v>
       </c>
       <c r="F42" s="3">
-        <v>29302000</v>
+        <v>32539000</v>
       </c>
       <c r="G42" s="3">
-        <v>31423900</v>
+        <v>28477000</v>
       </c>
       <c r="H42" s="3">
-        <v>28434800</v>
+        <v>30649600</v>
       </c>
       <c r="I42" s="3">
-        <v>23674400</v>
+        <v>27596900</v>
       </c>
       <c r="J42" s="3">
+        <v>22812600</v>
+      </c>
+      <c r="K42" s="3">
         <v>26011500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26355800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34545200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36693900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>42805700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39540100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>35042600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>32563700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>25206500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>23058400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>23893000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11799100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8588100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14306400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10267200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8580300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>42700</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>6875000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>7355000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>9198000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>808000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>756000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>715000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>34938000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>34774000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>44261000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>31502000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>33703600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>30806100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>25930900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,31 +4296,34 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>33801000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>31335000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>28496000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>26897000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>27336100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>27916500</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>28443200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4296,210 +4400,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1694000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1719000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1707000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1739000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1681100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1673000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1664000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1653600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1620300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1600200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1134700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1144800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1117900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1116700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1148900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1161600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1146700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1155300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1154600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1140900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1074200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1066500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1044800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>647400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>634400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>637800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>628700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>646500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>656700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>673600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>672800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>675300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8572000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8584000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8597000</v>
       </c>
-      <c r="F49" s="3">
-        <v>8612000</v>
-      </c>
       <c r="G49" s="3">
+        <v>9262000</v>
+      </c>
+      <c r="H49" s="3">
         <v>8627400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8642300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8682300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8699500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8728300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8746700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4595900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4597100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4599100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4601800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4604500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4607300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4610400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4614300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4618200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4622100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4626500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4631500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4637100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,31 +4816,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>7304000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>7904700</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>7826500</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>7746400</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4801,8 +4920,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>211785000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208855000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>215137000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208264000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>209124300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>207671700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>202956400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>200729800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>197955500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>204032900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149863600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>155107200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>151901200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>150622700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150481100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>142601100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>138626700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>139537000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>124577800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>119872800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>125500900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>121554900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120025200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,138 +5206,142 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4438000</v>
+        <v>164554000</v>
       </c>
       <c r="E57" s="3">
-        <v>4527000</v>
+        <v>159910000</v>
       </c>
       <c r="F57" s="3">
-        <v>4516000</v>
+        <v>167196000</v>
       </c>
       <c r="G57" s="3">
-        <v>4945900</v>
+        <v>163274000</v>
       </c>
       <c r="H57" s="3">
-        <v>4487900</v>
+        <v>164127800</v>
       </c>
       <c r="I57" s="3">
-        <v>4045800</v>
+        <v>162058400</v>
       </c>
       <c r="J57" s="3">
+        <v>159075200</v>
+      </c>
+      <c r="K57" s="3">
         <v>4377500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4476500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3743300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2174900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2127900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2067200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2042900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2166400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1719500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2095300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2033400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1762800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1562200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1388700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1346500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>3284000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5805000</v>
       </c>
       <c r="F58" s="3">
-        <v>5843000</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>5867000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>6898000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>8220500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>9203400</v>
       </c>
       <c r="J58" s="3">
+        <v>8059200</v>
+      </c>
+      <c r="K58" s="3">
         <v>4299100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5279,31 +5412,34 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5335,24 +5471,24 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>487600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>424900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>422400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>420000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5362,8 +5498,8 @@
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5380,31 +5516,34 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>170815000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>168639000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>176466000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>170654000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>172750000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>171651000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>167317400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,132 +5620,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11583000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11319000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11450000</v>
       </c>
-      <c r="F61" s="3">
-        <v>7674000</v>
-      </c>
       <c r="G61" s="3">
+        <v>8279000</v>
+      </c>
+      <c r="H61" s="3">
         <v>7123400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7416600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7462900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3220400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3459300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3017400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3443600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3485400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3500400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3499400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3498500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4382200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5458900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6321300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6321400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6986200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7002500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7655500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8476000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>458000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
+        <v>422000</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2320000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3003400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>2754100</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2754000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5683,8 +5828,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182909000</v>
+      </c>
+      <c r="E66" s="3">
         <v>180431000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>187968000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>181307000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182927800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>181870800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>177579200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>175411900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>172699000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>178238400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>131987500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>137203800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>134372400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>133902400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>134034600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>126413800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>122525700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>123591900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>108762000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>104156100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>109721100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>105863100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>104437700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,22 +6490,25 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>2011000</v>
       </c>
       <c r="F70" s="3">
         <v>2011000</v>
       </c>
       <c r="G70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="H70" s="3">
         <v>2010600</v>
@@ -6359,7 +6526,7 @@
         <v>2010600</v>
       </c>
       <c r="M70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="N70" s="3">
         <v>1750000</v>
@@ -6368,7 +6535,7 @@
         <v>1750000</v>
       </c>
       <c r="P70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="Q70" s="3">
         <v>1250000</v>
@@ -6392,7 +6559,7 @@
         <v>1250000</v>
       </c>
       <c r="X70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="Y70" s="3">
         <v>1231500</v>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18659000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18211000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17812000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17524000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17284400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16836800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16212100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15754000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15219800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14808600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14830700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14646400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14365900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14030200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13731900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13444400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13132400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12919300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12837400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12820900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12490200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12162300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11842400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26482000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25680000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25158000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24946000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24185900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23790300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23366600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23307400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23245900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23783900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16126000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16153400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15778800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15470300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15196500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14937300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14851000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14695100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14565800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14466600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14529800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14460300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14356000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>626000</v>
+        <v>721000</v>
       </c>
       <c r="E81" s="3">
-        <v>505000</v>
+        <v>655000</v>
       </c>
       <c r="F81" s="3">
-        <v>456200</v>
+        <v>531000</v>
       </c>
       <c r="G81" s="3">
-        <v>663800</v>
+        <v>482400</v>
       </c>
       <c r="H81" s="3">
-        <v>1516000</v>
+        <v>690000</v>
       </c>
       <c r="I81" s="3">
-        <v>675500</v>
+        <v>867000</v>
       </c>
       <c r="J81" s="3">
+        <v>702000</v>
+      </c>
+      <c r="K81" s="3">
         <v>739100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>620500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>531900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>339700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>434200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>476000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>438800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>428100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>451900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>353400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>473800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>250700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>473400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>461400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>452600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>462100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>525300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>505400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>805300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>332700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>302500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>335800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>360700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>328600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>307800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>92000</v>
+        <v>78000</v>
       </c>
       <c r="E83" s="3">
-        <v>95000</v>
+        <v>73000</v>
       </c>
       <c r="F83" s="3">
-        <v>92100</v>
+        <v>76000</v>
       </c>
       <c r="G83" s="3">
-        <v>92900</v>
+        <v>62300</v>
       </c>
       <c r="H83" s="3">
-        <v>181000</v>
+        <v>84800</v>
       </c>
       <c r="I83" s="3">
-        <v>92700</v>
+        <v>78200</v>
       </c>
       <c r="J83" s="3">
+        <v>56700</v>
+      </c>
+      <c r="K83" s="3">
         <v>79900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>103200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>154600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>57000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>58500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>59400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>59500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>116600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>58700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>58500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>58800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>56100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>56000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>30000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>67100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>33900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>37500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>35600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>36200</v>
       </c>
       <c r="AI83" s="3">
         <v>36200</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1354000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>608000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>800300</v>
       </c>
-      <c r="G89" s="3">
-        <v>1419600</v>
-      </c>
       <c r="H89" s="3">
-        <v>1685100</v>
+        <v>1420000</v>
       </c>
       <c r="I89" s="3">
-        <v>427800</v>
+        <v>1257000</v>
       </c>
       <c r="J89" s="3">
+        <v>428000</v>
+      </c>
+      <c r="K89" s="3">
         <v>953600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1137000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2483100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1295800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>696900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>486300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>537000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>994700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>664100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>131100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-394400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1130700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>746700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>66900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>413300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>550200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>521200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>484200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>716100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>442600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>337500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>111300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-87800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-66800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-46000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-55400</v>
-      </c>
       <c r="J91" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-87600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-46900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-93700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-51500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-58500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-51900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1386000</v>
+      </c>
+      <c r="E94" s="3">
         <v>5625000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>682900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1907400</v>
-      </c>
       <c r="H94" s="3">
-        <v>-6649500</v>
+        <v>-1907000</v>
       </c>
       <c r="I94" s="3">
-        <v>-1747700</v>
+        <v>-4903000</v>
       </c>
       <c r="J94" s="3">
+        <v>-1747000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>6219300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14038600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4195600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-50600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>967300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>4726700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-852100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>271300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>873700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>663000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>514500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-225000</v>
+        <v>225000</v>
       </c>
       <c r="E96" s="3">
-        <v>-221000</v>
+        <v>225000</v>
       </c>
       <c r="F96" s="3">
-        <v>-215700</v>
+        <v>221000</v>
       </c>
       <c r="G96" s="3">
-        <v>-216000</v>
+        <v>215700</v>
       </c>
       <c r="H96" s="3">
-        <v>-436400</v>
+        <v>216000</v>
       </c>
       <c r="I96" s="3">
-        <v>-220500</v>
+        <v>215000</v>
       </c>
       <c r="J96" s="3">
+        <v>221000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-205100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-209100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-369800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-156700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-154700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-141800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-141700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-142000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-141900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-141500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-284700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-143200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-145200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-132900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-139600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,132 +9209,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1852000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6438000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1520800</v>
       </c>
-      <c r="G100" s="3">
-        <v>408300</v>
-      </c>
       <c r="H100" s="3">
-        <v>5292500</v>
+        <v>408000</v>
       </c>
       <c r="I100" s="3">
-        <v>1617400</v>
+        <v>3676000</v>
       </c>
       <c r="J100" s="3">
+        <v>1617000</v>
+      </c>
+      <c r="K100" s="3">
         <v>1976000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2614400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>778700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-335900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7644300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3442900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-826800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18731700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4108700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3219600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>789600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E102" s="3">
         <v>83000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37600</v>
       </c>
-      <c r="G102" s="3">
-        <v>-79500</v>
-      </c>
       <c r="H102" s="3">
-        <v>328100</v>
+        <v>-79000</v>
       </c>
       <c r="I102" s="3">
-        <v>297500</v>
+        <v>30000</v>
       </c>
       <c r="J102" s="3">
+        <v>298000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-735600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>567500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>350700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>73900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-142100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>69200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>150500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-292800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>134400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-81500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-138100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-382800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>547500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-338200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>293800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>52600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>58500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,235 +656,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2245000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2212000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2152000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2060000</v>
       </c>
-      <c r="G8" s="3">
-        <v>2075300</v>
-      </c>
       <c r="H8" s="3">
+        <v>2075000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2185000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2452000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2285000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2072200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1781500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2393400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>928300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>958500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>992900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>970400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1017000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1038900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1001200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2152700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1120400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1185900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1229500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1237900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>982900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,35 +993,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2245000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2212000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2152000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2060000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2075300</v>
-      </c>
       <c r="H10" s="3">
+        <v>2075000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2185000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2452000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2285000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1091,8 +1100,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,13 +1353,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>27000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1363,8 +1382,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1441,49 +1460,52 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E15" s="3">
         <v>122000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>127000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>130000</v>
       </c>
-      <c r="G15" s="3">
-        <v>129300</v>
-      </c>
       <c r="H15" s="3">
+        <v>129000</v>
+      </c>
+      <c r="I15" s="3">
         <v>130000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>125000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-17600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-18400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-19600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-2700</v>
       </c>
       <c r="Q15" s="3">
         <v>-2700</v>
@@ -1492,61 +1514,64 @@
         <v>-2700</v>
       </c>
       <c r="S15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="T15" s="3">
         <v>-3100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-3900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-7800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-3900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="X15" s="3">
-        <v>-5100</v>
       </c>
       <c r="Y15" s="3">
         <v>-5100</v>
       </c>
       <c r="Z15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,112 +1605,116 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1266000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1247000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1321000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1206800</v>
-      </c>
       <c r="H17" s="3">
+        <v>1206000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1234000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1250000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1312000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>334800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>217800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>389500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>49600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>58100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>218700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>143600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>231100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>244600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>251400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>198200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>199300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>154300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>304800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>149600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>133700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>130100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>144200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>146800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>169100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1693,103 +1722,106 @@
         <v>946000</v>
       </c>
       <c r="E18" s="3">
+        <v>946000</v>
+      </c>
+      <c r="F18" s="3">
         <v>905000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>739000</v>
       </c>
-      <c r="G18" s="3">
-        <v>868500</v>
-      </c>
       <c r="H18" s="3">
+        <v>869000</v>
+      </c>
+      <c r="I18" s="3">
         <v>951000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1202000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>973000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1737400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1563700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2003900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>894200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>933800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>967200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>942400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>981400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>989300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>943100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1934000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>976800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>954800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>984900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>986500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>932600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>940400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>927100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>886200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>859200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>813800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1835,207 +1868,213 @@
         <v>37000</v>
       </c>
       <c r="E20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F20" s="3">
         <v>50000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>75000</v>
       </c>
-      <c r="G20" s="3">
-        <v>242800</v>
-      </c>
       <c r="H20" s="3">
+        <v>243000</v>
+      </c>
+      <c r="I20" s="3">
         <v>44000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>43000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>47000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-726700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-716200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-418900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-333800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-310200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-336800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-388900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-368800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-456300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-627000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-302600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-349900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-360900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1031000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>982000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>794000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>755000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1037000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1284000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1039000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1090500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>950700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>907600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>533300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>656900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>715600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>664700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>652400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>679900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>546400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>778700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>408400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>710700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>693900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>681600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>690500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>729400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>728600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>491800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>660700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>618100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>632000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>554100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>546300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,8 +2099,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2138,216 +2177,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>882000</v>
+      </c>
+      <c r="E23" s="3">
         <v>909000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>855000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>664000</v>
       </c>
-      <c r="G23" s="3">
-        <v>625700</v>
-      </c>
       <c r="H23" s="3">
+        <v>626000</v>
+      </c>
+      <c r="I23" s="3">
         <v>907000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1159000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>926000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1010600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>847500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>753000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>475300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>599900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>657000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>605600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>592500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>620500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>486900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>662100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>349700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>652200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>635100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>625500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>634500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>699400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>696400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>457900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>628700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>580500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>596400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>518300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>510100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E24" s="3">
         <v>188000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>133000</v>
       </c>
-      <c r="G24" s="3">
-        <v>143300</v>
-      </c>
       <c r="H24" s="3">
+        <v>144000</v>
+      </c>
+      <c r="I24" s="3">
         <v>217000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>292000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>224000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>245300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>173300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>113100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>142000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>161600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>147600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>145300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>149400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>114700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>152200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>80900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>159100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>155000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>152300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>151700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>153200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>170300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>266700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>105300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>220900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>224600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>215300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>169300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>179500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E26" s="3">
         <v>721000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>655000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>531000</v>
       </c>
-      <c r="G26" s="3">
-        <v>482400</v>
-      </c>
       <c r="H26" s="3">
+        <v>482000</v>
+      </c>
+      <c r="I26" s="3">
         <v>690000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>867000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>702000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>765400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>646600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>579700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>362200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>458000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>495500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>458100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>447200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>471100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>372100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>509900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>268800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>493100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>480100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>473300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>482700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>546200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>526100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>845800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>352600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>407800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>355900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>381100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>348900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>330600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E27" s="3">
         <v>674000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>626000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>505000</v>
       </c>
-      <c r="G27" s="3">
-        <v>456200</v>
-      </c>
       <c r="H27" s="3">
+        <v>456000</v>
+      </c>
+      <c r="I27" s="3">
         <v>664000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>841000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>676000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>739100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>620500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>531900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>339700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>434200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>476000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>438800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>428100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>451900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>353400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>473800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>250700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>473400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>461400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>452600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>462100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>525300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>505400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>805300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>332700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>387900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>335800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>360700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>328600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2848,12 +2908,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3083,207 +3152,213 @@
         <v>-37000</v>
       </c>
       <c r="E32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-50000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-75000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-242800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-44000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-43000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-47000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>726700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>716200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1250900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>418900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>333800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>310200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>336800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>388900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>368800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>456300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1271900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>627000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>302600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>349900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>360900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>393600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>321600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>316700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>793900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>474700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>311700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>346600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>289800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>341000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>303600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E33" s="3">
         <v>721000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>655000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>531000</v>
       </c>
-      <c r="G33" s="3">
-        <v>482400</v>
-      </c>
       <c r="H33" s="3">
+        <v>482000</v>
+      </c>
+      <c r="I33" s="3">
         <v>690000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>867000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>702000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>739100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>620500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>531900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>339700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>434200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>476000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>438800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>428100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>451900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>353400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>473800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>250700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>473400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>461400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>452600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>462100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>525300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>505400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>805300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>332700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>302500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>335800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>360700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>328600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E35" s="3">
         <v>721000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>655000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>531000</v>
       </c>
-      <c r="G35" s="3">
-        <v>482400</v>
-      </c>
       <c r="H35" s="3">
+        <v>482000</v>
+      </c>
+      <c r="I35" s="3">
         <v>690000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>867000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>702000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>739100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>620500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>531900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>339700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>434200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>476000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>438800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>428100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>451900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>353400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>473800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>250700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>473400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>461400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>452600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>462100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>525300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>505400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>805300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>332700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>302500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>335800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>360700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>328600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,243 +3760,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2216000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1778000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1695000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1731000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1768900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1848400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1817700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1517200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2255800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1688300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1411500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1337600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1479700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1410500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1259000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1552700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1489200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1354800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1298200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1432800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1818900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1271600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19207000</v>
+      </c>
+      <c r="E42" s="3">
         <v>24783000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25164000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32539000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28477000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30649600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27596900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22812600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26011500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26355800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>34545200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36693900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>42805700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39540100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>35042600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>32563700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>25206500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>23058400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23893000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11799100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8588100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14306400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10267200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E43" s="3">
         <v>69000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>68000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>68000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3987,35 +4079,38 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E44" s="3">
         <v>37000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>33000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>38000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>39000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>37100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>42700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>44600</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -4091,35 +4186,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6875000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7355000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9198000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>808000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>756000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>717000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>715000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21245000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34938000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34774000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44261000</v>
       </c>
-      <c r="G46" s="3">
-        <v>31502000</v>
-      </c>
       <c r="H46" s="3">
+        <v>31123000</v>
+      </c>
+      <c r="I46" s="3">
         <v>33703600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30806100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25930900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,35 +4400,38 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34051000</v>
+      </c>
+      <c r="E47" s="3">
         <v>33801000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31335000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28496000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26897000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27336100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27916500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28443200</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4403,216 +4507,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1694000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1719000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1707000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1739000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1681100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1673000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1664000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1653600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1620300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1600200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1134700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1144800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1117900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1116700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1148900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1161600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1146700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1155300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1154600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1140900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1074200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1066500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>647400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>634400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>637800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>628700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>646500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>656700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>673600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>672800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>675300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9383000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8572000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8584000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8597000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9262000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8627400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8642300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8682300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8699500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8728300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8746700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4595900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4597100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4599100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4601800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4604500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4607300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4610400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4614300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4618200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4622100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4626500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4631500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,13 +4935,16 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22000</v>
+        <v>8324000</v>
       </c>
       <c r="E52" s="3">
         <v>22000</v>
@@ -4834,20 +4953,20 @@
         <v>22000</v>
       </c>
       <c r="G52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="H52" s="3">
         <v>7304000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7904700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7826500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7746400</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4923,8 +5042,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208105000</v>
+      </c>
+      <c r="E54" s="3">
         <v>211785000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208855000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>215137000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208264000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>209124300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>207671700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>202956400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>200729800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>197955500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>204032900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149863600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>155107200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>151901200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150622700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>150481100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>142601100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>138626700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>139537000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>124577800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>119872800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>125500900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>121554900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,144 +5336,148 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>161095000</v>
+      </c>
+      <c r="E57" s="3">
         <v>164554000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>159910000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>167196000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>163274000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>164127800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>162058400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>159075200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4377500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4476500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3743300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2174900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2127900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2067200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2042900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2166400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1719500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2095300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2033400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1762800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1562200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1388700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2042000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3284000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5805000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5867000</v>
       </c>
-      <c r="G58" s="3">
-        <v>6898000</v>
-      </c>
       <c r="H58" s="3">
+        <v>6259000</v>
+      </c>
+      <c r="I58" s="3">
         <v>8220500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9203400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8059200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4299100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5415,8 +5548,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5441,8 +5577,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5474,24 +5610,24 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>487600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>424900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>422400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>420000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5501,8 +5637,8 @@
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5519,35 +5655,38 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>163137000</v>
+      </c>
+      <c r="E60" s="3">
         <v>170815000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>168639000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>176466000</v>
       </c>
-      <c r="G60" s="3">
-        <v>170654000</v>
-      </c>
       <c r="H60" s="3">
+        <v>169533000</v>
+      </c>
+      <c r="I60" s="3">
         <v>172750000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>171651000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>167317400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,139 +5762,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13122000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11583000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11319000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11450000</v>
       </c>
-      <c r="G61" s="3">
-        <v>8279000</v>
-      </c>
       <c r="H61" s="3">
+        <v>8918000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7123400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7416600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7462900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3220400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3459300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3017400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3443600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3485400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3500400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3499400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3498500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4382200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5458900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6321300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6321400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6986200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7002500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7655500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2762000</v>
+      </c>
+      <c r="E62" s="3">
         <v>458000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>422000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2320000</v>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3">
+        <v>2802000</v>
+      </c>
+      <c r="I62" s="3">
         <v>3003400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2754100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2754000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5831,8 +5976,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>179078000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182909000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>180431000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>187968000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>181307000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182927800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>181870800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>177579200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>175411900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>172699000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>178238400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>131987500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>137203800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>134372400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>133902400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>134034600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>126413800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>122525700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>123591900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>108762000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>104156100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>109721100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>105863100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6502,16 +6669,16 @@
         <v>2394000</v>
       </c>
       <c r="E70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="F70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>2011000</v>
       </c>
       <c r="G70" s="3">
         <v>2011000</v>
       </c>
       <c r="H70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="I70" s="3">
         <v>2010600</v>
@@ -6529,7 +6696,7 @@
         <v>2010600</v>
       </c>
       <c r="N70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="O70" s="3">
         <v>1750000</v>
@@ -6538,7 +6705,7 @@
         <v>1750000</v>
       </c>
       <c r="Q70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="R70" s="3">
         <v>1250000</v>
@@ -6562,7 +6729,7 @@
         <v>1250000</v>
       </c>
       <c r="Y70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="Z70" s="3">
         <v>1231500</v>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AK70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19079000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18659000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18211000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17812000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17524000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17284400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16836800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16212100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15754000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15219800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14808600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14830700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14646400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14365900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14030200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13731900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13444400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13132400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12919300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12837400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12820900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12490200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12162300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26633000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26482000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25680000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25158000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24946000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24185900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23790300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23366600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23307400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23245900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23783900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16126000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16153400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15778800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15470300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15196500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14937300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14851000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14695100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14565800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14466600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14529800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14460300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E81" s="3">
         <v>721000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>655000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>531000</v>
       </c>
-      <c r="G81" s="3">
-        <v>482400</v>
-      </c>
       <c r="H81" s="3">
+        <v>482000</v>
+      </c>
+      <c r="I81" s="3">
         <v>690000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>867000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>702000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>739100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>620500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>531900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>339700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>434200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>476000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>438800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>428100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>451900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>353400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>473800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>250700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>473400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>461400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>452600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>462100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>525300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>505400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>805300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>332700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>302500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>335800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>360700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>328600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E83" s="3">
         <v>78000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>73000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>76000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>62300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>84800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>56700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>103200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>154600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>57000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>58500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>59900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>59400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>59500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>116600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>58700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>58500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>58800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>56100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>30000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>67100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>33900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>32000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>37500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>35600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>36200</v>
       </c>
       <c r="AJ83" s="3">
         <v>36200</v>
       </c>
+      <c r="AK83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1676000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1354000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>608000</v>
       </c>
-      <c r="G89" s="3">
-        <v>800300</v>
-      </c>
       <c r="H89" s="3">
+        <v>800000</v>
+      </c>
+      <c r="I89" s="3">
         <v>1420000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1257000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>428000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>953600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1137000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2483100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1295800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>696900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>486300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>537000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>994700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>664100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>131100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-394400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1130700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>746700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>66900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>413300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>550200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>521200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>484200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>716100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>442600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>337500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>111300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,112 +8561,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-87800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-67000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-87600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-62000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-93700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-51500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-58500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-51900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2293000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5625000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="G94" s="3">
-        <v>682900</v>
-      </c>
       <c r="H94" s="3">
+        <v>683000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>6219300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14038600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4195600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>967300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4726700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-852100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>271300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>873700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>663000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>514500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,112 +9028,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>225000</v>
+        <v>224000</v>
       </c>
       <c r="E96" s="3">
         <v>225000</v>
       </c>
       <c r="F96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="G96" s="3">
         <v>221000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>215700</v>
       </c>
       <c r="H96" s="3">
         <v>216000</v>
       </c>
       <c r="I96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="J96" s="3">
         <v>215000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>221000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-205100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-209100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-369800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-156700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-154700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-141800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-142000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-141900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-141500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-284700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-143200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-145200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-132900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-134400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,112 +9454,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4276000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1852000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6438000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1520800</v>
-      </c>
       <c r="H100" s="3">
+        <v>-1521000</v>
+      </c>
+      <c r="I100" s="3">
         <v>408000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3676000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1617000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1976000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2614400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>778700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-335900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7644300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3442900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-826800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18731700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4108700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3219600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>789600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,8 +9590,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9420,108 +9668,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-307000</v>
+      </c>
+      <c r="E102" s="3">
         <v>438000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>83000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-37600</v>
-      </c>
       <c r="H102" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-79000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>298000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-735600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>567500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>350700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-142100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>69200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>150500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-292800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>63500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>134400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-81500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-138100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-382800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>547500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>293800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>52600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>22800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>58500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,241 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2245000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2212000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2152000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2060000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2075000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2185000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2452000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2285000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2072200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1781500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2393400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>928300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>958500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>992900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>970400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1017000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1038900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1001200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2152700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1120400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1185900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1229500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>982900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -996,38 +1002,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2245000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2212000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2152000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2060000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2075000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2185000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2452000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2285000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,17 +1372,20 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>27000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1385,8 +1404,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1463,52 +1482,55 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E15" s="3">
         <v>129000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>122000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>130000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>129000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>130000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>125000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>113000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-17600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-18400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-19600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-2700</v>
       </c>
       <c r="R15" s="3">
         <v>-2700</v>
@@ -1517,61 +1539,64 @@
         <v>-2700</v>
       </c>
       <c r="T15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U15" s="3">
         <v>-3100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-3900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-7800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-3900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>-5100</v>
       </c>
       <c r="Z15" s="3">
         <v>-5100</v>
       </c>
       <c r="AA15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1299000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1266000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1247000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1321000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1206000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1234000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1250000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1312000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>334800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>217800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>389500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>35600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>58100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>218700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>143600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>231100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>244600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>251400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>198200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>199300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>154300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>304800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>149600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>133700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>130100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>144200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>146800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>169100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>946000</v>
+        <v>797000</v>
       </c>
       <c r="E18" s="3">
         <v>946000</v>
       </c>
       <c r="F18" s="3">
+        <v>946000</v>
+      </c>
+      <c r="G18" s="3">
         <v>905000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>739000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>869000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>951000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1202000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>973000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1737400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1563700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2003900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>894200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>933800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>967200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>942400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>981400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>989300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>943100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1934000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>976800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>954800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>984900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>986500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>932600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>940400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>927100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>886200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>859200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>813800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,222 +1891,229 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>37000</v>
+        <v>36000</v>
       </c>
       <c r="E20" s="3">
         <v>37000</v>
       </c>
       <c r="F20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="G20" s="3">
         <v>50000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>75000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>243000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>44000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>43000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>47000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-726700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-716200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-418900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-333800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-310200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-336800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-388900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-368800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-456300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-627000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-302600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-349900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-360900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1038000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1031000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>982000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>794000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>755000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1037000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1284000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1039000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1090500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>950700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>907600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>533300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>656900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>715600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>664700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>652400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>679900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>546400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>778700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>408400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>710700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>693900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>681600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>690500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>729400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>728600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>491800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>660700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>618100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>632000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>554100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>546300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,8 +2141,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2180,222 +2219,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E23" s="3">
         <v>882000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>909000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>855000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>664000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>626000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>907000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1159000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>926000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1010600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>847500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>753000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>475300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>599900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>657000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>605600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>592500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>620500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>486900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>662100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>349700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>652200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>635100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>625500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>634500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>699400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>696400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>457900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>628700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>580500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>596400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>518300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>510100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E24" s="3">
         <v>201000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>188000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>133000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>144000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>217000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>292000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>224000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>245300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>173300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>113100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>142000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>161600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>147600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>145300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>149400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>114700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>152200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>80900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>159100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>155000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>152300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>151700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>153200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>170300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>266700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>105300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>220900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>224600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>215300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>169300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>179500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E26" s="3">
         <v>681000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>721000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>655000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>531000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>482000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>690000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>867000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>702000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>765400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>646600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>579700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>362200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>458000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>495500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>458100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>447200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>471100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>372100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>509900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>268800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>493100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>480100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>473300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>482700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>546200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>526100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>845800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>352600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>407800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>355900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>381100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>330600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>547000</v>
+      </c>
+      <c r="E27" s="3">
         <v>644000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>674000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>626000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>505000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>456000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>664000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>841000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>676000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>739100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>620500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>531900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>339700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>434200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>476000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>438800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>428100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>451900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>353400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>473800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>250700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>473400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>461400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>452600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>462100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>525300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>505400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>805300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>332700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>387900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>335800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>360700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>307800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2953,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2911,12 +2971,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,222 +3209,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-37000</v>
+        <v>-36000</v>
       </c>
       <c r="E32" s="3">
         <v>-37000</v>
       </c>
       <c r="F32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-50000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-75000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-243000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-44000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-43000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-47000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>726700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>716200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1250900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>418900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>333800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>310200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>336800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>388900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>368800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>456300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1271900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>627000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>302600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>349900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>360900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>393600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>321600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>316700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>793900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>474700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>311700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>346600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>289800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>303600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E33" s="3">
         <v>681000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>721000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>655000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>531000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>482000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>690000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>867000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>702000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>739100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>620500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>531900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>339700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>434200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>476000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>438800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>428100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>451900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>353400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>473800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>250700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>473400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>461400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>452600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>462100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>525300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>505400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>805300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>332700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>302500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>335800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>360700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>307800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E35" s="3">
         <v>681000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>721000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>655000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>531000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>482000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>690000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>867000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>702000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>739100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>620500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>531900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>339700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>434200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>476000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>438800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>428100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>451900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>353400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>473800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>250700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>473400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>461400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>452600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>462100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>525300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>505400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>805300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>332700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>302500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>335800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>360700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>307800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,252 +3846,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1909000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2216000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1778000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1695000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1731000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1768900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1848400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1817700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1517200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2255800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1688300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1411500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1337600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1479700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1410500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1259000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1552700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1489200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1354800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1298200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1432800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1818900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20970000</v>
+      </c>
+      <c r="E42" s="3">
         <v>19207000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>24783000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25164000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32539000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28477000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30649600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27596900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22812600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26011500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26355800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>34545200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>36693900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>42805700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>39540100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>35042600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>32563700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>25206500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23058400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>23893000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>11799100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8588100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14306400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10267200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E43" s="3">
         <v>72000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>69000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>68000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68000</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4082,38 +4174,41 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E44" s="3">
         <v>35000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>37000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>33000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>38000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>39000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>37100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>42700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>44600</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -4189,38 +4284,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9394000</v>
+      </c>
+      <c r="E45" s="3">
         <v>22000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6875000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7355000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9198000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>808000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>756000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>717000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>715000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32575000</v>
+      </c>
+      <c r="E46" s="3">
         <v>21245000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34938000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34774000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>44261000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31123000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>33703600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>30806100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25930900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,38 +4504,41 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35137000</v>
+      </c>
+      <c r="E47" s="3">
         <v>34051000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>33801000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31335000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28496000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26897000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27336100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27916500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28443200</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4510,222 +4614,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1661000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1705000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1694000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1719000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1707000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1739000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1681100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1673000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1664000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1653600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1620300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1134700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1144800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1117900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1116700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1148900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1161600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1146700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1155300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1154600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1140900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1074200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1066500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>647400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>634400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>637800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>628700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>646500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>656700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>673600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>672800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>675300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8558000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9383000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8572000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8584000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8597000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9262000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8627400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8642300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8682300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8699500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8728300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8746700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4595900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4597100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4599100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4601800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4604500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4607300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4610400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4614300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4618200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4622100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4626500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4631500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,16 +5054,19 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8324000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>22000</v>
       </c>
       <c r="F52" s="3">
         <v>22000</v>
@@ -4956,20 +5075,20 @@
         <v>22000</v>
       </c>
       <c r="H52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I52" s="3">
         <v>7304000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7904700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7826500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7746400</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5045,8 +5164,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>210321000</v>
+      </c>
+      <c r="E54" s="3">
         <v>208105000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>211785000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208855000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>215137000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>208264000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>209124300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>207671700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>202956400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>200729800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>197955500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>204032900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>149863600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>155107200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>151901200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>150622700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>150481100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>142601100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>138626700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>139537000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>124577800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>119872800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>125500900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>121554900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,150 +5466,154 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>165409000</v>
+      </c>
+      <c r="E57" s="3">
         <v>161095000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>164554000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159910000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>167196000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>163274000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>164127800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>162058400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>159075200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4377500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4476500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3743300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2174900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2127900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2067200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2042900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2166400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1719500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2095300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2033400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1762800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1562200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1388700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2205000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2042000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3284000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5805000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5867000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6259000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8220500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9203400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8059200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4299100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -5551,8 +5684,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5580,8 +5716,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5613,24 +5749,24 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>487600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>424900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>422400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>420000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5640,8 +5776,8 @@
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
@@ -5658,38 +5794,41 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>170779000</v>
+      </c>
+      <c r="E60" s="3">
         <v>163137000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>170815000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>168639000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>176466000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>169533000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>172750000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>171651000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>167317400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,145 +5904,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10496000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13122000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11583000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11319000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11450000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8918000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7123400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7416600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7462900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3220400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3459300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3017400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3443600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3485400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3500400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3499400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3498500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4382200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5458900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6321300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6321400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6986200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7002500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7655500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
         <v>2762000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>458000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>422000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
         <v>2802000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3003400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2754100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2754000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5979,8 +6124,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181330000</v>
+      </c>
+      <c r="E66" s="3">
         <v>179078000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>182909000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>180431000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>187968000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>181307000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>182927800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>181870800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>177579200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>175411900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>172699000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>178238400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>131987500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>137203800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>134372400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>133902400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>134034600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>126413800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>122525700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>123591900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>108762000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>104156100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>109721100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>105863100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6672,16 +6839,16 @@
         <v>2394000</v>
       </c>
       <c r="F70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="G70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="G70" s="3">
-        <v>2011000</v>
       </c>
       <c r="H70" s="3">
         <v>2011000</v>
       </c>
       <c r="I70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="J70" s="3">
         <v>2010600</v>
@@ -6699,7 +6866,7 @@
         <v>2010600</v>
       </c>
       <c r="O70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="P70" s="3">
         <v>1750000</v>
@@ -6708,7 +6875,7 @@
         <v>1750000</v>
       </c>
       <c r="R70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="S70" s="3">
         <v>1250000</v>
@@ -6732,7 +6899,7 @@
         <v>1250000</v>
       </c>
       <c r="Z70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="AA70" s="3">
         <v>1231500</v>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AL70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19405000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19079000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18659000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18211000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17812000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17524000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17284400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16836800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16212100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15754000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15219800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14808600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14830700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14646400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14365900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14030200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13731900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13444400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13132400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12919300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12837400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12820900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12490200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12162300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26597000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26633000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26482000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25680000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25158000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24946000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24185900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23790300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23366600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23307400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23245900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23783900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16126000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16153400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15778800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15470300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15196500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14937300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14851000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14695100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14565800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14466600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14529800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14460300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E81" s="3">
         <v>681000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>721000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>655000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>531000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>482000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>690000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>867000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>702000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>739100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>620500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>531900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>339700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>434200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>476000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>438800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>428100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>451900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>353400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>473800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>250700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>473400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>461400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>452600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>462100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>525300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>505400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>805300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>332700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>302500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>335800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>360700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>307800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E83" s="3">
         <v>77000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>78000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>73000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>76000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>62300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>84800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>56700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>103200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>154600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>58000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>57000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>58500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>59100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>59900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>59400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>59500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>116600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>58700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>58500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>58800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>56000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>30000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>67100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>33900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>35600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>36200</v>
       </c>
       <c r="AK83" s="3">
         <v>36200</v>
       </c>
+      <c r="AL83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>635000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1676000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1354000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>608000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>800000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1420000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1257000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>428000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>953600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1137000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2483100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1295800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>696900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>486300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>537000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>994700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>664100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>131100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-394400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1130700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>746700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>66900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>413300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>550200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>521200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>484200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>716100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>442600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>337500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>111300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,115 +8781,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-88000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-87600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-46900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-31700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-93700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-51500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-58500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2132000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2293000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5625000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>683000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>6219300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14038600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4195600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>967300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4726700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-852100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>271300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>873700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>663000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>514500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,115 +9261,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E96" s="3">
         <v>224000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>225000</v>
       </c>
       <c r="F96" s="3">
         <v>225000</v>
       </c>
       <c r="G96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="H96" s="3">
         <v>221000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>216000</v>
       </c>
       <c r="I96" s="3">
         <v>216000</v>
       </c>
       <c r="J96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="K96" s="3">
         <v>215000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>221000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-205100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-209100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-369800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-156700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-154700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-141800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-141700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-142000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-141900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-141500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-284700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-143200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-145200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-132900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4276000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1852000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6438000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1521000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>408000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3676000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1617000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1976000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2614400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>778700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-335900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7644300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3442900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-826800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>18731700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4108700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3219600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>789600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,8 +9841,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-307000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>438000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-79000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>298000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-735600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>567500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>350700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>73900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-142100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>69200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>150500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-292800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>63500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>134400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-81500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-138100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-382800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>547500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>293800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>52600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>22800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>58500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,247 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2176000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2245000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2212000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2152000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2060000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2075000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2185000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2452000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2285000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2072200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1781500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2393400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>928300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>958500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>992900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>970400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1017000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1038900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1001200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2152700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1120400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1185900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1229500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>982900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1005,41 +1011,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2176000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2245000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2212000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2152000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2060000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2075000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2185000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2452000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2285000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,20 +1391,23 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>27000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1407,8 +1426,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1485,55 +1504,58 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E15" s="3">
         <v>130000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>129000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>122000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>127000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>130000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>129000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>125000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>113000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-17600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-18400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-19600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>-2700</v>
       </c>
       <c r="S15" s="3">
         <v>-2700</v>
@@ -1542,61 +1564,64 @@
         <v>-2700</v>
       </c>
       <c r="U15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="V15" s="3">
         <v>-3100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-3900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-7800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>-5100</v>
       </c>
       <c r="AA15" s="3">
         <v>-5100</v>
       </c>
       <c r="AB15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1379000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1299000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1266000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1247000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1321000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1206000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1234000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1250000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1312000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>334800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>217800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>389500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>58100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>218700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>143600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>231100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>244600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>251400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>198200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>199300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>154300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>304800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>149600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>133700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>130100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>144200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>146800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>169100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E18" s="3">
         <v>797000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>946000</v>
       </c>
       <c r="F18" s="3">
         <v>946000</v>
       </c>
       <c r="G18" s="3">
+        <v>946000</v>
+      </c>
+      <c r="H18" s="3">
         <v>905000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>739000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>869000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>951000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1202000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>973000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1737400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1563700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2003900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>894200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>933800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>967200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>942400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>981400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>989300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>943100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1934000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>976800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>954800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>984900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>986500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>932600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>940400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>927100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>886200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>859200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>813800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,228 +1924,235 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>36000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>37000</v>
       </c>
       <c r="F20" s="3">
         <v>37000</v>
       </c>
       <c r="G20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H20" s="3">
         <v>50000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>75000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>243000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>44000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>43000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-726700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-716200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-418900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-333800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-310200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-336800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-388900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-368800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-456300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-627000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-302600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-349900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-360900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="E21" s="3">
         <v>891000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1038000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1031000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>982000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>794000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>755000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1037000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1284000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1039000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1090500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>950700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>907600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>533300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>656900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>715600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>664700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>652400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>679900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>546400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>778700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>408400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>710700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>693900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>681600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>690500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>729400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>728600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>491800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>660700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>618100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>632000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>554100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>546300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,8 +2183,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2222,228 +2261,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>935000</v>
+      </c>
+      <c r="E23" s="3">
         <v>761000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>882000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>909000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>855000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>664000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>626000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>907000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1159000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>926000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1010600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>847500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>753000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>475300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>599900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>657000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>605600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>592500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>620500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>486900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>662100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>349700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>652200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>635100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>625500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>634500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>699400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>696400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>457900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>628700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>580500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>596400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>518300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>510100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E24" s="3">
         <v>177000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>201000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>188000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>133000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>144000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>217000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>292000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>224000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>245300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>173300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>113100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>142000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>161600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>147600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>145300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>149400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>114700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>152200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>80900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>159100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>155000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>152300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>151700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>153200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>170300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>266700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>105300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>220900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>224600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>215300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>169300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>179500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E26" s="3">
         <v>584000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>681000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>721000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>655000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>531000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>482000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>690000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>867000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>702000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>765400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>646600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>579700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>362200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>458000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>495500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>458100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>447200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>471100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>372100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>509900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>268800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>493100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>480100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>473300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>482700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>546200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>526100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>845800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>352600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>407800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>355900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>381100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>348900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>330600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>679000</v>
+      </c>
+      <c r="E27" s="3">
         <v>547000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>644000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>674000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>626000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>505000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>456000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>664000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>841000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>676000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>739100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>620500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>531900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>339700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>434200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>476000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>438800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>428100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>451900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>353400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>473800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>250700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>473400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>461400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>452600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>462100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>525300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>505400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>805300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>332700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>387900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>335800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>360700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>328600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>307800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2956,8 +3016,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2974,12 +3034,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,228 +3278,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-36000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-37000</v>
       </c>
       <c r="F32" s="3">
         <v>-37000</v>
       </c>
       <c r="G32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-50000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-75000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-243000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-44000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-43000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>726700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>716200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1250900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>418900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>333800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>310200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>336800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>388900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>368800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>456300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1271900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>627000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>302600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>349900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>360900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>393600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>321600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>316700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>793900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>474700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>311700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>346600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>289800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>341000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>303600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E33" s="3">
         <v>584000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>681000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>721000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>655000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>531000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>482000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>690000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>867000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>702000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>739100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>620500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>531900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>339700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>434200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>476000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>438800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>428100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>451900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>353400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>473800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>250700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>473400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>461400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>452600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>462100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>525300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>505400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>805300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>332700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>302500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>335800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>360700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>328600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>307800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E35" s="3">
         <v>584000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>681000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>721000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>655000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>531000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>482000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>690000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>867000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>702000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>739100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>620500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>531900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>339700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>434200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>476000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>438800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>428100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>451900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>353400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>473800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>250700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>473400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>461400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>452600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>462100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>525300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>505400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>805300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>332700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>302500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>335800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>360700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>328600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>307800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,261 +3932,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2128000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2109000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1909000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2216000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1778000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1695000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1731000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1768900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1848400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1817700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1517200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2255800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1688300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1411500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1337600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1479700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1410500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1259000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1552700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1489200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1354800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1298200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1432800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1818900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19635000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20970000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19207000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24783000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25164000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>32539000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28477000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30649600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27596900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22812600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26011500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26355800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>34545200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>36693900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>42805700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>39540100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>35042600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>32563700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>25206500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>23058400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>23893000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11799100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8588100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>14306400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10267200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E43" s="3">
         <v>68000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>72000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>69000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>61000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>68000</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4177,41 +4269,44 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E44" s="3">
         <v>34000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>37000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>38000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>39000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>37100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>42700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>44600</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -4287,41 +4382,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10022000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9394000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6875000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7355000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9198000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>808000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>756000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>717000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>715000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4397,41 +4495,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31886000</v>
+      </c>
+      <c r="E46" s="3">
         <v>32575000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21245000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34938000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34774000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>44261000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31123000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33703600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30806100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25930900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,41 +4608,44 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35568000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35137000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34051000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>33801000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31335000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28496000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26897000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27336100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27916500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28443200</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4617,228 +4721,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1646000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1661000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1705000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1694000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1719000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1707000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1739000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1681100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1673000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1664000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1653600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1620300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1600200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1134700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1144800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1117900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1116700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1148900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1161600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1146700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1155300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1154600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1140900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1074200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1066500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>647400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>634400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>637800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>628700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>646500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>656700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>673600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>672800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>675300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8549000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8558000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9383000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8572000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8584000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8597000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9262000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8627400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8642300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8682300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8699500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8728300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8746700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4595900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4597100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4599100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4601800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4604500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4607300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4610400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4614300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4618200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4622100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4626500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4631500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,8 +5173,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5066,10 +5185,10 @@
         <v>16000</v>
       </c>
       <c r="E52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F52" s="3">
         <v>8324000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>22000</v>
       </c>
       <c r="G52" s="3">
         <v>22000</v>
@@ -5078,20 +5197,20 @@
         <v>22000</v>
       </c>
       <c r="I52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="J52" s="3">
         <v>7304000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7904700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7826500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7746400</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5167,8 +5286,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>211584000</v>
+      </c>
+      <c r="E54" s="3">
         <v>210321000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208105000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>211785000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208855000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>215137000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>208264000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>209124300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>207671700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>202956400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>200729800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>197955500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>204032900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>149863600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>155107200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>151901200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>150622700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>150481100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>142601100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>138626700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>139537000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>124577800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>119872800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>125500900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>121554900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,156 +5596,160 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>164453000</v>
+      </c>
+      <c r="E57" s="3">
         <v>165409000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>161095000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>164554000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>159910000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>167196000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>163274000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>164127800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>162058400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>159075200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4377500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4476500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3743300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2174900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2127900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2067200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2042900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2166400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1719500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2095300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2033400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1762800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1562200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1388700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2625000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2205000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2042000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3284000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5805000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5867000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6259000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8220500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9203400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8059200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4299100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5687,8 +5820,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5719,8 +5855,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5752,24 +5888,24 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>487600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>424900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>422400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>420000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5779,8 +5915,8 @@
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
@@ -5797,41 +5933,44 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>170627000</v>
+      </c>
+      <c r="E60" s="3">
         <v>170779000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>163137000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>170815000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>168639000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>176466000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>169533000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>172750000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>171651000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>167317400</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,151 +6046,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12380000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10496000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13122000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11583000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11319000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11450000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8918000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7123400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7416600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7462900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3220400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3459300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3017400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3443600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3485400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3500400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3499400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3498500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4382200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5458900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6321300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6321400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6986200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7002500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7655500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>2762000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>458000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>422000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>2802000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3003400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2754100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2754000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6127,8 +6272,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>183059000</v>
+      </c>
+      <c r="E66" s="3">
         <v>181330000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>179078000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182909000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>180431000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>187968000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>181307000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>182927800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>181870800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>177579200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>175411900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>172699000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>178238400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>131987500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>137203800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>134372400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>133902400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>134034600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>126413800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>122525700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>123591900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>108762000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>104156100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>109721100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>105863100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6991,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6842,16 +7009,16 @@
         <v>2394000</v>
       </c>
       <c r="G70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="H70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>2011000</v>
       </c>
       <c r="I70" s="3">
         <v>2011000</v>
       </c>
       <c r="J70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="K70" s="3">
         <v>2010600</v>
@@ -6869,7 +7036,7 @@
         <v>2010600</v>
       </c>
       <c r="P70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="Q70" s="3">
         <v>1750000</v>
@@ -6878,7 +7045,7 @@
         <v>1750000</v>
       </c>
       <c r="S70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="T70" s="3">
         <v>1250000</v>
@@ -6902,7 +7069,7 @@
         <v>1250000</v>
       </c>
       <c r="AA70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="AB70" s="3">
         <v>1231500</v>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AM70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19870000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19405000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19079000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18659000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18211000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17812000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17524000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17284400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16836800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16212100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15754000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15219800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14808600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14830700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14646400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14365900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14030200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13731900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13444400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13132400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12919300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12837400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12820900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12490200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12162300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26131000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26597000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26633000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26482000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25680000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25158000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24946000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24185900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23790300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23366600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23307400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23245900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23783900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16126000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16153400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15778800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15470300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15196500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14937300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14851000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14695100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14565800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14466600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14529800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14460300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E81" s="3">
         <v>584000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>681000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>721000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>655000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>531000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>482000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>690000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>867000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>702000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>739100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>620500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>531900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>339700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>434200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>476000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>438800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>428100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>451900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>353400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>473800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>250700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>473400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>461400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>452600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>462100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>525300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>505400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>805300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>332700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>302500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>335800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>360700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>328600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>307800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,118 +8169,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E83" s="3">
         <v>80000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>78000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>73000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>76000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>62300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>84800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>56700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>103200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>154600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>58000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>57000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>58500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>59100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>59900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>59400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>59500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>116600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>58700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>58500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>58800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>56100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>56000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>30000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>67100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>33900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>32000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>37500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>35600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>36200</v>
       </c>
       <c r="AL83" s="3">
         <v>36200</v>
       </c>
+      <c r="AM83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>844000</v>
+      </c>
+      <c r="E89" s="3">
         <v>635000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1676000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1354000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>608000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>800000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1420000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1257000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>428000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>953600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1137000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2483100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1295800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>696900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>486300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>537000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>994700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>664100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>131100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-394400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1130700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>746700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>66900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>413300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>550200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>521200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>484200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>716100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>442600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>337500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>111300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,118 +9001,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-35000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-88000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-67000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-87600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-62000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-93700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-51500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-58500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-853000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2132000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2293000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5625000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>683000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6219300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14038600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4195600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>967300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4726700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-852100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>271300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>873700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>663000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>514500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,118 +9494,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E96" s="3">
         <v>225000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>224000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>225000</v>
       </c>
       <c r="G96" s="3">
         <v>225000</v>
       </c>
       <c r="H96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="I96" s="3">
         <v>221000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>216000</v>
       </c>
       <c r="J96" s="3">
         <v>216000</v>
       </c>
       <c r="K96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="L96" s="3">
         <v>215000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>221000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-205100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-209100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-369800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-156700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-154700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-141800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-141700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-142000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-141900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-141500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-284700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-143200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-145200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-132900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,118 +9944,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1697000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4276000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1852000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6438000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1521000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>408000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3676000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1617000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1976000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2614400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>778700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-335900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>7644300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3442900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-826800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>18731700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4108700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3219600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>789600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,8 +10092,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9922,114 +10170,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>200000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-307000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>438000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-79000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>298000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-735600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>567500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>350700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>73900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-142100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>150500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-292800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>63500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>134400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-81500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-138100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-382800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>547500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>293800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>52600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>22800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>58500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2350000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2388000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2271000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2176000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2245000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2212000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2152000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2060000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2075000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2185000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2452000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2285000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2072200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1781500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2393400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>928300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>958500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>992900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>970400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1017000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1038900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1001200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2152700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1120400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1185900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1229500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>982900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1023,47 +1029,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2350000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2388000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2271000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2176000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2245000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2212000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2152000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2060000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2075000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2185000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2452000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2285000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1139,8 +1148,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +1429,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1427,8 +1446,8 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>27000</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
@@ -1451,8 +1470,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1529,8 +1548,11 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1538,52 +1560,52 @@
         <v>122000</v>
       </c>
       <c r="E15" s="3">
+        <v>122000</v>
+      </c>
+      <c r="F15" s="3">
         <v>124000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>130000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>129000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>122000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>127000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>129000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>130000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>125000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>113000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-17600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-19600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-1300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>-2700</v>
       </c>
       <c r="U15" s="3">
         <v>-2700</v>
@@ -1592,61 +1614,64 @@
         <v>-2700</v>
       </c>
       <c r="W15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="X15" s="3">
         <v>-3100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>-5100</v>
       </c>
       <c r="AC15" s="3">
         <v>-5100</v>
       </c>
       <c r="AD15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1340000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1305000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1379000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1299000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1266000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1247000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1321000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1206000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1234000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1250000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1312000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>334800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>217800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>389500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>49600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>58100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>218700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>143600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>231100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>244600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>251400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>198200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>199300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>154300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>304800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>149600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>133700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>130100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>144200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>146800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>169100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1048000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>966000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>797000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>919000</v>
+      </c>
+      <c r="I18" s="3">
         <v>946000</v>
       </c>
-      <c r="H18" s="3">
-        <v>946000</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>905000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>739000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>869000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>951000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1202000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>973000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1737400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1563700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2003900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>894200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>933800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>967200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>942400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>981400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>989300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>943100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1934000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>976800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>954800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>984900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>986500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>932600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>940400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>927100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>886200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>859200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>813800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,240 +1990,247 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>23000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>36000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>37000</v>
       </c>
       <c r="H20" s="3">
         <v>37000</v>
       </c>
       <c r="I20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J20" s="3">
         <v>50000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>75000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>243000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>44000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>43000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>47000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-726700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-716200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-418900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-333800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-310200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-336800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-388900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-368800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-456300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-627000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-302600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-349900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-360900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1093000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1147000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1059000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>891000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1038000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1011000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1031000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>982000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>794000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>755000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1037000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1284000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1039000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1090500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>950700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>907600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>533300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>656900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>715600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>664700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>652400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>679900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>546400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>778700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>408400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>710700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>693900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>681600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>690500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>729400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>728600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>491800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>660700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>618100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>632000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>554100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>546300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,240 +2345,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>971000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1025000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>935000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>761000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>882000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>909000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>855000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>664000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>626000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>907000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1159000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>926000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1010600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>847500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>753000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>475300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>599900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>657000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>605600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>592500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>620500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>486900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>662100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>349700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>652200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>635100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>625500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>634500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>699400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>696400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>457900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>628700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>580500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>596400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>518300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>510100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E24" s="3">
         <v>233000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>219000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>177000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>201000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>188000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>133000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>144000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>217000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>292000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>224000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>245300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>173300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>113100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>142000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>161600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>147600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>145300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>149400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>152200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>80900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>159100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>155000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>152300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>151700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>153200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>170300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>266700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>105300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>220900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>224600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>215300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>169300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>179500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E26" s="3">
         <v>792000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>716000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>584000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>681000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>721000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>655000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>531000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>482000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>690000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>867000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>702000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>765400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>646600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>579700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>362200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>458000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>495500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>458100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>447200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>471100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>372100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>509900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>268800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>493100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>480100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>473300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>482700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>546200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>526100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>845800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>352600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>407800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>355900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>381100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>348900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>330600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>718000</v>
+      </c>
+      <c r="E27" s="3">
         <v>754000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>679000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>547000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>644000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>674000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>626000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>505000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>456000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>664000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>841000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>676000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>739100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>620500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>531900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>339700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>434200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>476000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>438800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>428100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>451900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>353400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>473800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>250700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>473400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>461400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>452600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>462100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>525300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>505400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>805300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>332700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>387900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>335800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>360700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>328600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>307800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3082,8 +3142,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3100,12 +3160,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,240 +3416,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-23000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-36000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-37000</v>
       </c>
       <c r="H32" s="3">
         <v>-37000</v>
       </c>
       <c r="I32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-50000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-75000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-243000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-44000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-43000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-47000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>726700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>716200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1250900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>418900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>333800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>310200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>336800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>388900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>368800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>456300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1271900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>627000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>302600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>349900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>360900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>393600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>321600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>316700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>793900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>474700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>311700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>346600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>289800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>341000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>303600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E33" s="3">
         <v>792000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>716000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>584000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>681000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>721000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>655000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>531000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>482000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>690000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>867000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>702000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>739100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>620500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>531900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>339700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>434200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>476000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>438800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>428100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>451900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>353400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>473800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>250700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>473400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>461400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>452600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>462100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>525300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>505400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>805300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>332700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>302500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>335800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>360700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>328600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>307800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E35" s="3">
         <v>792000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>716000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>584000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>681000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>721000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>655000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>531000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>482000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>690000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>867000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>702000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>739100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>620500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>531900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>339700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>434200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>476000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>438800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>428100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>451900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>353400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>473800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>250700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>473400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>461400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>452600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>462100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>525300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>505400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>805300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>332700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>302500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>335800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>360700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>328600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>307800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,279 +4104,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18769000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1950000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2128000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2109000</v>
       </c>
-      <c r="G41" s="3">
-        <v>1909000</v>
-      </c>
       <c r="H41" s="3">
+        <v>20782000</v>
+      </c>
+      <c r="I41" s="3">
         <v>2216000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1778000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1695000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1731000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1768900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1848400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1817700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1517200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2255800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1688300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1411500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1337600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1479700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1410500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1259000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1552700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1489200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1354800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1298200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1432800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1818900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E42" s="3">
         <v>17099000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19635000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20970000</v>
       </c>
-      <c r="G42" s="3">
-        <v>19207000</v>
-      </c>
       <c r="H42" s="3">
+        <v>356000</v>
+      </c>
+      <c r="I42" s="3">
         <v>24783000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25164000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32539000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28477000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30649600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27596900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22812600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26011500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>26355800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>34545200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>36693900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>42805700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>39540100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>35042600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>32563700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>25206500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>23058400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>23893000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>11799100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8588100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14306400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10267200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E43" s="3">
         <v>68000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>71000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>72000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>69000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>67000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>61000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>68000</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4367,47 +4459,50 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E44" s="3">
         <v>37000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>30000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>34000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>37000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>38000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>39000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>37100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>44600</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -4483,47 +4578,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>795000</v>
+        <v>8310000</v>
       </c>
       <c r="E45" s="3">
+        <v>8523000</v>
+      </c>
+      <c r="F45" s="3">
         <v>210000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9394000</v>
       </c>
-      <c r="G45" s="3">
-        <v>6773000</v>
-      </c>
       <c r="H45" s="3">
+        <v>6877000</v>
+      </c>
+      <c r="I45" s="3">
         <v>6875000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7355000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9198000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>808000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>756000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>717000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>715000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19949000</v>
+        <v>28456000</v>
       </c>
       <c r="E46" s="3">
+        <v>27677000</v>
+      </c>
+      <c r="F46" s="3">
         <v>22074000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32575000</v>
       </c>
-      <c r="G46" s="3">
-        <v>27996000</v>
-      </c>
       <c r="H46" s="3">
+        <v>28643000</v>
+      </c>
+      <c r="I46" s="3">
         <v>34938000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34774000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44261000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31123000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33703600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30806100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25930900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,47 +4816,50 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38616000</v>
+      </c>
+      <c r="E47" s="3">
         <v>38611000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>37234000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35137000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>35607000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33801000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>31335000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28496000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26897000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27336100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>27916500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28443200</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4831,240 +4935,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1813000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1621000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1646000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1661000</v>
       </c>
-      <c r="G48" s="3">
-        <v>1705000</v>
-      </c>
       <c r="H48" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1694000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1719000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1707000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1739000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1681100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1673000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1664000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1653600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1620300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1600200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1134700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1144800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1117900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1116700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1148900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1161600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1146700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1155300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1154600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1140900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1074200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1066500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>647400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>634400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>637800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>628700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>646500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>656700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>673600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>672800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>675300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8948000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8539000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8549000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8558000</v>
       </c>
-      <c r="G49" s="3">
-        <v>9383000</v>
-      </c>
       <c r="H49" s="3">
+        <v>9053000</v>
+      </c>
+      <c r="I49" s="3">
         <v>8572000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8584000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8597000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9262000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8627400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8642300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8682300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8699500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8728300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8746700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4595900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4597100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4599100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4601800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4604500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4607300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4610400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4614300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4618200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4622100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4626500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4631500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,25 +5411,28 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7744000</v>
+        <v>16000</v>
       </c>
       <c r="E52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F52" s="3">
         <v>8162000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>22000</v>
       </c>
       <c r="I52" s="3">
         <v>22000</v>
@@ -5322,20 +5441,20 @@
         <v>22000</v>
       </c>
       <c r="K52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="L52" s="3">
         <v>7304000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7904700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7826500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7746400</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5411,8 +5530,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>213510000</v>
+      </c>
+      <c r="E54" s="3">
         <v>211277000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>211584000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>210321000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208105000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>211785000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>208855000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>215137000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>208264000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>209124300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>207671700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>202956400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>200729800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>197955500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>204032900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>149863600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>155107200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>151901200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>150622700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>150481100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>142601100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>138626700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>139537000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>124577800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>119872800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>125500900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>121554900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,168 +5856,172 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>166909000</v>
+      </c>
+      <c r="E57" s="3">
         <v>163426000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>164453000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>165409000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>161095000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>164554000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>159910000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>167196000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>163274000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>164127800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>162058400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>159075200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4377500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4476500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3743300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2174900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2127900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2067200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2042900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2166400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1719500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2095300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2033400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1762800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1562200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1388700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2756000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2539000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2625000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2205000</v>
       </c>
-      <c r="G58" s="3">
-        <v>2042000</v>
-      </c>
       <c r="H58" s="3">
+        <v>1882000</v>
+      </c>
+      <c r="I58" s="3">
         <v>3284000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5805000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5867000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6259000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8220500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9203400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8059200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4299100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5959,8 +6092,11 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5997,8 +6133,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -6030,24 +6166,24 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>487600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>424900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>422400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>420000</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6057,8 +6193,8 @@
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -6075,47 +6211,50 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>171812000</v>
+      </c>
+      <c r="E60" s="3">
         <v>168769000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>169930000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>170779000</v>
       </c>
-      <c r="G60" s="3">
-        <v>165229000</v>
-      </c>
       <c r="H60" s="3">
+        <v>165009000</v>
+      </c>
+      <c r="I60" s="3">
         <v>170815000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>168639000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>176466000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>169533000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>172750000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>171651000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>167317400</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,163 +6330,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11410000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12928000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12380000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10496000</v>
       </c>
-      <c r="G61" s="3">
-        <v>13122000</v>
-      </c>
       <c r="H61" s="3">
+        <v>13282000</v>
+      </c>
+      <c r="I61" s="3">
         <v>11583000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11319000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11450000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8918000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7123400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7416600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7462900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3220400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3459300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3017400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3443600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3485400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3500400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3499400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3498500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4382200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5458900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6321300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6321400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6986200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7002500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7655500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1057000</v>
+      </c>
+      <c r="E62" s="3">
         <v>798000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>697000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3">
-        <v>670000</v>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3">
+        <v>730000</v>
+      </c>
+      <c r="I62" s="3">
         <v>458000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>422000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>2802000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3003400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2754100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2754000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6423,8 +6568,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>184333000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182549000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>183059000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>181330000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>179078000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182909000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>180431000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>187968000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>181307000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>182927800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>181870800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>177579200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>175411900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>172699000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>178238400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>131987500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>137203800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>134372400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>133902400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>134034600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>126413800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>122525700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>123591900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>108762000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>104156100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>109721100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>105863100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,13 +7325,16 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>2394000</v>
+        <v>2834000</v>
       </c>
       <c r="E70" s="3">
         <v>2394000</v>
@@ -7182,16 +7349,16 @@
         <v>2394000</v>
       </c>
       <c r="I70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="J70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>2011000</v>
       </c>
       <c r="K70" s="3">
         <v>2011000</v>
       </c>
       <c r="L70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="M70" s="3">
         <v>2010600</v>
@@ -7209,7 +7376,7 @@
         <v>2010600</v>
       </c>
       <c r="R70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="S70" s="3">
         <v>1750000</v>
@@ -7218,7 +7385,7 @@
         <v>1750000</v>
       </c>
       <c r="U70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="V70" s="3">
         <v>1250000</v>
@@ -7242,7 +7409,7 @@
         <v>1250000</v>
       </c>
       <c r="AC70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="AD70" s="3">
         <v>1231500</v>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AO70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20882000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20392000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19870000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19405000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19079000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18659000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18211000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17812000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17524000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17284400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16836800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16212100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15754000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15219800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14808600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14830700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14646400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14365900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14030200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13731900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13444400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13132400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12919300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12837400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12820900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12490200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12162300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26343000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26334000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26131000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26597000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26633000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26482000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25680000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25158000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24946000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24185900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23790300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23366600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23307400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23245900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23783900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16126000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16153400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15778800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15470300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15196500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14937300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14851000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14695100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14565800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14466600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14529800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14460300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E81" s="3">
         <v>792000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>716000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>584000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>681000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>721000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>655000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>531000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>482000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>690000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>867000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>702000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>739100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>620500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>531900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>339700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>434200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>476000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>438800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>428100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>451900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>353400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>473800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>250700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>473400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>461400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>452600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>462100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>525300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>505400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>805300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>332700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>302500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>335800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>360700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>328600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>307800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E83" s="3">
         <v>76000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>79000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>80000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>78000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>73000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>76000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>62300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>84800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>56700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>103200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>154600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>58000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>57000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>58500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>59100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>59900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>59500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>116600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>58700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>58500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>58800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>56100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>56000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>30000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>67100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>33900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>37500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>35600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>36200</v>
       </c>
       <c r="AN83" s="3">
         <v>36200</v>
       </c>
+      <c r="AO83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>523000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1001000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>844000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>635000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1676000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1354000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>608000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>800000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1420000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1257000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>428000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>953600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2483100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1295800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>696900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>486300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>537000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>994700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>664100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>131100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-394400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1130700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>746700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>66900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>413300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>550200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>521200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>484200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>716100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>442600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>337500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>111300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,124 +9441,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-85000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-66000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-87600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-62000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-93700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-51500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-58500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3832000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-853000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2132000</v>
       </c>
-      <c r="G94" s="3">
-        <v>2293000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-6903000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5625000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>683000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6219300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>14038600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4195600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-50600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>967300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4726700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-852100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>271300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>873700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>663000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>514500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,124 +9960,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E96" s="3">
         <v>233000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>213000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>225000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>224000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>225000</v>
       </c>
       <c r="I96" s="3">
         <v>225000</v>
       </c>
       <c r="J96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="K96" s="3">
         <v>221000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>216000</v>
       </c>
       <c r="L96" s="3">
         <v>216000</v>
       </c>
       <c r="M96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="N96" s="3">
         <v>215000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>221000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-205100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-209100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-369800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-156700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-154700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-141800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-141700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-142000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-141900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-141500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-284700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-143200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-145200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-132900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,124 +10434,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1255000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1180000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>28000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1697000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4276000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1852000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6438000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1521000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>408000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3676000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1617000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1976000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2614400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>778700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-335900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7644300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3442900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-826800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18731700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4108700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3219600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>789600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,8 +10594,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10424,120 +10672,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2054000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-178000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-307000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-9503000</v>
+      </c>
+      <c r="I102" s="3">
         <v>438000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>83000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-79000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>298000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-735600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>567500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>350700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>73900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-142100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>150500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-292800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>63500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>134400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-81500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-138100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-382800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>547500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>293800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>52600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>22800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>58500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>47800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2301000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2350000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2388000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2271000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2176000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2245000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2212000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2152000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2060000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2075000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2185000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2452000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2285000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2072200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1781500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2393400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>928300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>958500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>992900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>970400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1017000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1038900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1001200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2152700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1120400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1185900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1229500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>982900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1032,50 +1038,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2301000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2350000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2388000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2271000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2176000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2245000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2212000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2152000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2060000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2075000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2185000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2452000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2285000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1151,8 +1160,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1448,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1473,8 +1492,8 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1551,64 +1570,67 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>122000</v>
+        <v>97000</v>
       </c>
       <c r="E15" s="3">
         <v>122000</v>
       </c>
       <c r="F15" s="3">
+        <v>122000</v>
+      </c>
+      <c r="G15" s="3">
         <v>124000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>130000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>129000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>122000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>127000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>130000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>129000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>130000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>125000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>113000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-18400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-19600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-1300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>-2700</v>
       </c>
       <c r="V15" s="3">
         <v>-2700</v>
@@ -1617,61 +1639,64 @@
         <v>-2700</v>
       </c>
       <c r="X15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>-5100</v>
       </c>
       <c r="AD15" s="3">
         <v>-5100</v>
       </c>
       <c r="AE15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1377000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1340000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1305000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1379000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1326000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1266000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1247000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1321000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1206000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1234000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1250000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1312000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>334800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>217800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>389500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>35600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>49600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>58100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>218700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>143600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>231100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>244600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>251400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>198200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>199300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>154300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>304800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>149600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>133700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>130100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>144200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>146800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>169100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>895000</v>
+      </c>
+      <c r="E18" s="3">
         <v>973000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1048000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>966000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>797000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>919000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>946000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>905000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>739000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>869000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>951000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1202000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>973000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1737400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1563700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2003900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>894200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>933800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>967200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>942400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>981400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>989300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>943100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1934000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>976800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>954800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>984900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>986500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>932600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>940400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>927100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>886200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>859200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>813800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,246 +2023,253 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>23000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>36000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>37000</v>
       </c>
       <c r="I20" s="3">
         <v>37000</v>
       </c>
       <c r="J20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K20" s="3">
         <v>50000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>75000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>243000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>44000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>43000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>47000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-726700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-716200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-418900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-333800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-310200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-336800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-388900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-368800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-456300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-627000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-302600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-349900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-360900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>960000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1093000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1147000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1059000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>891000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1011000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1031000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>982000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>794000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>755000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1037000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1284000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1039000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1090500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>950700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>907600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>533300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>656900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>715600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>664700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>652400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>679900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>546400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>778700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>408400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>710700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>693900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>681600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>690500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>729400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>728600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>491800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>660700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>618100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>632000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>554100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>546300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,8 +2309,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2348,246 +2387,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E23" s="3">
         <v>971000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1025000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>935000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>761000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>882000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>909000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>855000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>664000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>626000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>907000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1159000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>926000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1010600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>847500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>753000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>475300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>599900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>657000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>605600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>592500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>620500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>486900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>662100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>349700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>652200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>635100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>625500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>634500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>699400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>696400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>457900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>628700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>580500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>596400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>518300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>510100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E24" s="3">
         <v>212000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>233000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>219000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>177000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>201000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>188000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>133000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>144000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>217000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>292000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>224000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>245300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>173300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>113100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>142000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>161600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>147600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>145300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>149400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>114700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>152200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>80900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>159100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>155000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>152300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>151700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>153200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>170300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>266700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>105300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>220900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>224600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>215300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>169300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>179500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E26" s="3">
         <v>759000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>792000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>716000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>584000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>681000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>721000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>655000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>531000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>482000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>690000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>867000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>702000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>765400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>646600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>579700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>362200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>458000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>495500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>458100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>447200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>471100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>372100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>509900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>268800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>493100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>480100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>473300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>482700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>546200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>526100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>845800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>352600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>407800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>355900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>381100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>348900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>330600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>620000</v>
+      </c>
+      <c r="E27" s="3">
         <v>718000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>754000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>679000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>547000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>644000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>674000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>626000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>505000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>456000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>664000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>841000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>676000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>739100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>620500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>531900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>339700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>434200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>476000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>438800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>428100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>451900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>353400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>473800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>250700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>473400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>461400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>452600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>462100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>525300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>505400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>805300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>387900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>335800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>360700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>328600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>307800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3163,12 +3223,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3485,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-23000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-36000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-37000</v>
       </c>
       <c r="I32" s="3">
         <v>-37000</v>
       </c>
       <c r="J32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-50000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-75000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-243000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-44000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-43000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-47000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>726700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>716200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1250900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>418900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>333800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>310200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>336800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>388900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>368800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>456300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1271900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>627000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>302600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>349900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>360900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>393600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>321600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>316700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>793900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>474700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>311700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>346600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>289800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>341000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>303600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E33" s="3">
         <v>759000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>792000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>716000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>584000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>681000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>721000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>655000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>531000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>482000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>690000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>867000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>702000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>739100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>620500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>531900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>339700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>434200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>476000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>438800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>428100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>451900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>353400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>473800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>250700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>473400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>461400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>452600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>462100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>525300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>505400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>805300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>302500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>335800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>360700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>328600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>307800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E35" s="3">
         <v>759000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>792000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>716000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>584000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>681000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>721000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>655000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>531000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>482000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>690000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>867000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>702000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>739100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>620500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>531900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>339700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>434200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>476000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>438800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>428100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>451900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>353400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>473800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>250700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>473400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>461400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>452600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>462100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>525300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>505400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>805300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>302500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>335800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>360700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>328600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>307800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,288 +4190,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16348000</v>
+      </c>
+      <c r="E41" s="3">
         <v>18769000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1950000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2128000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2109000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20782000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2216000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1778000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1695000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1731000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1768900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1848400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1817700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1517200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2255800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1688300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1411500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1337600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1479700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1410500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1259000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1552700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1489200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1354800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1298200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1432800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1818900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>309000</v>
+      </c>
+      <c r="E42" s="3">
         <v>342000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17099000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19635000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20970000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>356000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24783000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25164000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32539000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>28477000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30649600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27596900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22812600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>26011500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26355800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>34545200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>36693900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>42805700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>39540100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>35042600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>32563700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>25206500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>23058400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>23893000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11799100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8588100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14306400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10267200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E43" s="3">
         <v>75000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>68000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>68000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>72000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>69000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>67000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>68000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>63000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>68000</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4462,50 +4554,53 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E44" s="3">
         <v>35000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>37000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>34000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>37000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>37100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>42700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>44600</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -4581,50 +4676,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9393000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8310000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8523000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>210000</v>
       </c>
-      <c r="G45" s="3">
-        <v>9394000</v>
-      </c>
       <c r="H45" s="3">
+        <v>7868000</v>
+      </c>
+      <c r="I45" s="3">
         <v>6877000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6875000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7355000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9198000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>808000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>756000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>717000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>715000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26150000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28456000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27677000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22074000</v>
       </c>
-      <c r="G46" s="3">
-        <v>32575000</v>
-      </c>
       <c r="H46" s="3">
+        <v>31049000</v>
+      </c>
+      <c r="I46" s="3">
         <v>28643000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34938000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34774000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44261000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31123000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33703600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30806100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25930900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,50 +4920,53 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40556000</v>
+      </c>
+      <c r="E47" s="3">
         <v>38616000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>38611000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37234000</v>
       </c>
-      <c r="G47" s="3">
-        <v>35137000</v>
-      </c>
       <c r="H47" s="3">
+        <v>36663000</v>
+      </c>
+      <c r="I47" s="3">
         <v>35607000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33801000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31335000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28496000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26897000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>27336100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27916500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28443200</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4938,246 +5042,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1716000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1813000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1621000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1646000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1661000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1909000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1694000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1719000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1707000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1739000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1681100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1673000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1664000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1653600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1620300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1600200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1134700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1144800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1117900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1116700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1148900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1161600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1146700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1155300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1154600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1140900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1074200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1066500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>647400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>634400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>637800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>628700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>646500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>656700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>673600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>672800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>675300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8520000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8948000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8539000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8549000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8558000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9053000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8572000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8584000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8597000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9262000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8627400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8642300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8682300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8699500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8728300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8746700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4595900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4597100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4599100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4601800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4604500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4607300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4610400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4614300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4618200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4622100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4626500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4631500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,8 +5530,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5426,16 +5545,16 @@
         <v>16000</v>
       </c>
       <c r="F52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G52" s="3">
         <v>8162000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>22000</v>
       </c>
       <c r="J52" s="3">
         <v>22000</v>
@@ -5444,20 +5563,20 @@
         <v>22000</v>
       </c>
       <c r="L52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="M52" s="3">
         <v>7304000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7904700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7826500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7746400</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5533,8 +5652,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>214736000</v>
+      </c>
+      <c r="E54" s="3">
         <v>213510000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>211277000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>211584000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>210321000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>208105000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>211785000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>208855000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>215137000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>208264000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>209124300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>207671700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>202956400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200729800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>197955500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>204032900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>149863600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>155107200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>151901200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>150622700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>150481100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>142601100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>138626700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>139537000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>124577800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>119872800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>125500900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>121554900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,174 +5986,178 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>163741000</v>
+      </c>
+      <c r="E57" s="3">
         <v>166909000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>163426000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>164453000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>165409000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>161095000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>164554000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>159910000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167196000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>163274000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>164127800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>162058400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>159075200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4377500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4476500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3743300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2174900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2127900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2067200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2042900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2166400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1719500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2095300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2033400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1762800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1562200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1388700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8276000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2756000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2539000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2625000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2205000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1882000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3284000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5805000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5867000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6259000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8220500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9203400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8059200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4299100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -6095,8 +6228,11 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6136,8 +6272,8 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -6169,24 +6305,24 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>487600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>424900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>422400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>420000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6196,8 +6332,8 @@
       <c r="AI59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ59" s="3">
-        <v>0</v>
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK59" s="3">
         <v>0</v>
@@ -6214,50 +6350,53 @@
       <c r="AO59" s="3">
         <v>0</v>
       </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174548000</v>
+      </c>
+      <c r="E60" s="3">
         <v>171812000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>168769000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169930000</v>
       </c>
-      <c r="G60" s="3">
-        <v>170779000</v>
-      </c>
       <c r="H60" s="3">
+        <v>170079000</v>
+      </c>
+      <c r="I60" s="3">
         <v>165009000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>170815000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>168639000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>176466000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>169533000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>172750000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>171651000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>167317400</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,169 +6472,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11175000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11410000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12928000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12380000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10496000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13282000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11583000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11319000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11450000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8918000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7123400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7416600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7462900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3220400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3459300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3017400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3443600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3485400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3500400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3499400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3498500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4382200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5458900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6321300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6321400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6986200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7002500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7655500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>989000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1057000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>798000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>697000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H62" s="3">
+        <v>700000</v>
+      </c>
+      <c r="I62" s="3">
         <v>730000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>458000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>422000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>2802000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3003400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2754100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2754000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6571,8 +6716,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>186764000</v>
+      </c>
+      <c r="E66" s="3">
         <v>184333000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>182549000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>183059000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>181330000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>179078000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>182909000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>180431000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>187968000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>181307000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>182927800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>181870800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>177579200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>175411900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>172699000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>178238400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>131987500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>137203800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>134372400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>133902400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>134034600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>126413800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>122525700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>123591900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>108762000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>104156100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>109721100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>105863100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,16 +7492,19 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2434000</v>
+      </c>
+      <c r="E70" s="3">
         <v>2834000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>2394000</v>
       </c>
       <c r="F70" s="3">
         <v>2394000</v>
@@ -7352,16 +7519,16 @@
         <v>2394000</v>
       </c>
       <c r="J70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="K70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="K70" s="3">
-        <v>2011000</v>
       </c>
       <c r="L70" s="3">
         <v>2011000</v>
       </c>
       <c r="M70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="N70" s="3">
         <v>2010600</v>
@@ -7379,7 +7546,7 @@
         <v>2010600</v>
       </c>
       <c r="S70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="T70" s="3">
         <v>1750000</v>
@@ -7388,7 +7555,7 @@
         <v>1750000</v>
       </c>
       <c r="V70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="W70" s="3">
         <v>1250000</v>
@@ -7412,7 +7579,7 @@
         <v>1250000</v>
       </c>
       <c r="AD70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="AE70" s="3">
         <v>1231500</v>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AP70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21476000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20882000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20392000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19870000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19405000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19079000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18659000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18211000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17812000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17524000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17284400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16836800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16212100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15754000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15219800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14808600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14830700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14646400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14365900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14030200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13731900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13444400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13132400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12919300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12837400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12820900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12490200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12162300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25538000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26343000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26334000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26131000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26597000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26633000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26482000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25680000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25158000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24946000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24185900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23790300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23366600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23307400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23245900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23783900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16126000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16153400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15778800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15470300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15196500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14937300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14851000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14695100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14565800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14466600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14529800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14460300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E81" s="3">
         <v>759000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>792000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>716000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>584000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>681000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>721000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>655000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>531000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>482000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>690000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>867000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>702000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>739100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>620500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>531900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>339700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>434200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>476000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>438800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>428100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>451900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>353400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>473800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>250700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>473400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>461400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>452600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>462100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>525300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>505400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>805300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>302500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>335800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>360700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>328600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>307800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E83" s="3">
         <v>81000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>76000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>73000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>76000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>62300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>84800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>56700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>79900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>103200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>154600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>58000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>57000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>58500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>59100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>59400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>59500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>116600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>58700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>58500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>58800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>56100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>56000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>30000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>32200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>67100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>32000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>37500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>35600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>36200</v>
       </c>
       <c r="AO83" s="3">
         <v>36200</v>
       </c>
+      <c r="AP83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E89" s="3">
         <v>523000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1001000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>844000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>635000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1676000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1354000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>608000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>800000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1420000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1257000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>428000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>953600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1137000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2483100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1295800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>696900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>486300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>537000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>994700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>664100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>131100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-394400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1130700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>746700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>66900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>413300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>550200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>521200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>484200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>716100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>442600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>337500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>111300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9661,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-85000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-88000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-87600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-59800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-62000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-42700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-31000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-93700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-51500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-58500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4324000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3832000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-853000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2132000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-6903000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5625000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>683000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6219300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>14038600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4195600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-50600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>967300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>4726700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-852100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>271300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>873700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>663000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>514500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,127 +10193,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E96" s="3">
         <v>228000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>233000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>213000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>225000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>224000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>225000</v>
       </c>
       <c r="J96" s="3">
         <v>225000</v>
       </c>
       <c r="K96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="L96" s="3">
         <v>221000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>216000</v>
       </c>
       <c r="M96" s="3">
         <v>216000</v>
       </c>
       <c r="N96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="O96" s="3">
         <v>215000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>221000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-205100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-209100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-369800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-156700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-154700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-141800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-141700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-142000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-141900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-141500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-284700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-143200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-145200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-132900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,127 +10679,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1255000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1180000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>28000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1697000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4276000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1852000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6438000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1521000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>408000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3676000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1617000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1976000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2614400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>778700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-335900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7644300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3442900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-826800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>18731700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4108700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3219600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>789600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,8 +10845,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10675,123 +10923,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2421000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2054000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-178000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="G102" s="3">
-        <v>200000</v>
-      </c>
       <c r="H102" s="3">
+        <v>1983000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-9503000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>438000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>83000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-79000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>298000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-735600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>567500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>350700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>73900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-142100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>150500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-292800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>63500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>134400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-138100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-382800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>547500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>293800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>52600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>22800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>58500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>47800</v>
       </c>
     </row>
